--- a/research/traditional_assets/database/data/iceland/iceland_air_transport.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_air_transport.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.19</v>
+        <v>-0.0339</v>
       </c>
       <c r="G2">
-        <v>-0.2628087831655993</v>
+        <v>-0.06115248921991376</v>
       </c>
       <c r="H2">
-        <v>-0.2628087831655993</v>
+        <v>-0.06115248921991376</v>
       </c>
       <c r="I2">
-        <v>-0.4023330283623056</v>
+        <v>-0.03279498235985889</v>
       </c>
       <c r="J2">
-        <v>-0.4023330283623056</v>
+        <v>-0.03279498235985889</v>
       </c>
       <c r="K2">
-        <v>-148.2</v>
+        <v>-69.3</v>
       </c>
       <c r="L2">
-        <v>-0.338975297346752</v>
+        <v>-0.05433163465307722</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>217</v>
+        <v>313.6</v>
       </c>
       <c r="V2">
-        <v>0.4318407960199005</v>
+        <v>0.57425379967039</v>
       </c>
       <c r="W2">
-        <v>-0.5033967391304348</v>
+        <v>-0.3111374678054082</v>
       </c>
       <c r="X2">
-        <v>0.09830635221689736</v>
+        <v>0.1749729598701272</v>
       </c>
       <c r="Y2">
-        <v>-0.6017030913473321</v>
+        <v>-0.4861104276755354</v>
       </c>
       <c r="Z2">
-        <v>0.8929738562091505</v>
+        <v>1.892714052530049</v>
       </c>
       <c r="AA2">
-        <v>-0.3592728758169935</v>
+        <v>-0.1794851848975273</v>
       </c>
       <c r="AB2">
-        <v>0.06263468243940401</v>
+        <v>0.0967888216349128</v>
       </c>
       <c r="AC2">
-        <v>-0.4219075582563975</v>
+        <v>-0.2762740065324401</v>
       </c>
       <c r="AD2">
-        <v>519.7</v>
+        <v>792.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>519.7</v>
+        <v>792.3</v>
       </c>
       <c r="AG2">
-        <v>302.7</v>
+        <v>478.6999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.5084132263744864</v>
+        <v>0.5919754931261206</v>
       </c>
       <c r="AI2">
-        <v>0.6667094291212317</v>
+        <v>0.7081694672863782</v>
       </c>
       <c r="AJ2">
-        <v>0.3759314456035768</v>
+        <v>0.4671155347384855</v>
       </c>
       <c r="AK2">
-        <v>0.5381333333333335</v>
+        <v>0.5945106805762543</v>
       </c>
       <c r="AL2">
-        <v>11.5</v>
+        <v>32.22</v>
       </c>
       <c r="AM2">
-        <v>7.21</v>
+        <v>25.753</v>
       </c>
       <c r="AN2">
-        <v>-6.28415961305925</v>
+        <v>22.8328530259366</v>
       </c>
       <c r="AO2">
-        <v>-15.29565217391304</v>
+        <v>-1.298261949099938</v>
       </c>
       <c r="AP2">
-        <v>-3.660217654171706</v>
+        <v>13.79538904899135</v>
       </c>
       <c r="AQ2">
-        <v>-24.39667128987518</v>
+        <v>-1.624276783287384</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.19</v>
+        <v>-0.0339</v>
       </c>
       <c r="G3">
-        <v>-0.2628087831655993</v>
+        <v>-0.04597009795497509</v>
       </c>
       <c r="H3">
-        <v>-0.2628087831655993</v>
+        <v>-0.04597009795497509</v>
       </c>
       <c r="I3">
-        <v>-0.4023330283623056</v>
+        <v>-0.002689465543907888</v>
       </c>
       <c r="J3">
-        <v>-0.4023330283623056</v>
+        <v>-0.002689465543907888</v>
       </c>
       <c r="K3">
-        <v>-148.2</v>
+        <v>-30.3</v>
       </c>
       <c r="L3">
-        <v>-0.338975297346752</v>
+        <v>-0.02603540127169617</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,198 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>217</v>
+        <v>290.1</v>
       </c>
       <c r="V3">
-        <v>0.4318407960199005</v>
+        <v>0.6215984572530534</v>
       </c>
       <c r="W3">
-        <v>-0.5033967391304348</v>
+        <v>-0.1157814291173099</v>
       </c>
       <c r="X3">
-        <v>0.09830635221689736</v>
+        <v>0.1555080653055878</v>
       </c>
       <c r="Y3">
-        <v>-0.6017030913473321</v>
+        <v>-0.2712894944228977</v>
       </c>
       <c r="Z3">
-        <v>0.8929738562091505</v>
+        <v>2.062012756909993</v>
       </c>
       <c r="AA3">
-        <v>-0.3592728758169935</v>
+        <v>-0.005545712260807936</v>
       </c>
       <c r="AB3">
-        <v>0.06263468243940401</v>
+        <v>0.09666376952670391</v>
       </c>
       <c r="AC3">
-        <v>-0.4219075582563975</v>
+        <v>-0.1022094817875119</v>
       </c>
       <c r="AD3">
-        <v>519.7</v>
+        <v>618.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>519.7</v>
+        <v>618.8</v>
       </c>
       <c r="AG3">
-        <v>302.7</v>
+        <v>328.6999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.5084132263744864</v>
+        <v>0.5700598802395209</v>
       </c>
       <c r="AI3">
-        <v>0.6667094291212317</v>
+        <v>0.6832284420889919</v>
       </c>
       <c r="AJ3">
-        <v>0.3759314456035768</v>
+        <v>0.4132511943676138</v>
       </c>
       <c r="AK3">
-        <v>0.5381333333333335</v>
+        <v>0.5339506172839505</v>
       </c>
       <c r="AL3">
-        <v>11.5</v>
+        <v>24.7</v>
       </c>
       <c r="AM3">
-        <v>7.21</v>
+        <v>19.11</v>
       </c>
       <c r="AN3">
-        <v>-6.28415961305925</v>
+        <v>8.131406044678055</v>
       </c>
       <c r="AO3">
-        <v>-15.29565217391304</v>
+        <v>-0.1267206477732793</v>
       </c>
       <c r="AP3">
-        <v>-3.660217654171706</v>
+        <v>4.319316688567674</v>
       </c>
       <c r="AQ3">
-        <v>-24.39667128987518</v>
+        <v>-0.1637885923600209</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fly Play hf. (ICSE:PLAY)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Air Transport</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>-0.2193375111906893</v>
+      </c>
+      <c r="H4">
+        <v>-0.2193375111906893</v>
+      </c>
+      <c r="I4">
+        <v>-0.3464637421665175</v>
+      </c>
+      <c r="J4">
+        <v>-0.3464637421665175</v>
+      </c>
+      <c r="K4">
+        <v>-39</v>
+      </c>
+      <c r="L4">
+        <v>-0.3491495076096687</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>23.5</v>
+      </c>
+      <c r="V4">
+        <v>0.2959697732997481</v>
+      </c>
+      <c r="W4">
+        <v>-0.5064935064935064</v>
+      </c>
+      <c r="X4">
+        <v>0.1944378544346667</v>
+      </c>
+      <c r="Y4">
+        <v>-0.7009313609281731</v>
+      </c>
+      <c r="Z4">
+        <v>1.020091324200913</v>
+      </c>
+      <c r="AA4">
+        <v>-0.3534246575342466</v>
+      </c>
+      <c r="AB4">
+        <v>0.09691387374312169</v>
+      </c>
+      <c r="AC4">
+        <v>-0.4503385312773683</v>
+      </c>
+      <c r="AD4">
+        <v>173.5</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>173.5</v>
+      </c>
+      <c r="AG4">
+        <v>150</v>
+      </c>
+      <c r="AH4">
+        <v>0.6860419137999209</v>
+      </c>
+      <c r="AI4">
+        <v>0.8141717503519474</v>
+      </c>
+      <c r="AJ4">
+        <v>0.6538796861377506</v>
+      </c>
+      <c r="AK4">
+        <v>0.7911392405063291</v>
+      </c>
+      <c r="AL4">
+        <v>7.52</v>
+      </c>
+      <c r="AM4">
+        <v>6.643</v>
+      </c>
+      <c r="AN4">
+        <v>-4.190821256038648</v>
+      </c>
+      <c r="AO4">
+        <v>-5.146276595744681</v>
+      </c>
+      <c r="AP4">
+        <v>-3.623188405797102</v>
+      </c>
+      <c r="AQ4">
+        <v>-5.825681168146922</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/iceland/iceland_air_transport.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_air_transport.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="icse_iceair" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0339</v>
+        <v>-0.00026</v>
       </c>
       <c r="G2">
-        <v>-0.06115248921991376</v>
+        <v>0.03087723303464414</v>
       </c>
       <c r="H2">
-        <v>-0.06115248921991376</v>
+        <v>0.03087723303464414</v>
       </c>
       <c r="I2">
-        <v>-0.03279498235985889</v>
+        <v>0.01820672336053878</v>
       </c>
       <c r="J2">
-        <v>-0.03279498235985889</v>
+        <v>0.01567801178268617</v>
       </c>
       <c r="K2">
-        <v>-69.3</v>
+        <v>-1.800000000000004</v>
       </c>
       <c r="L2">
-        <v>-0.05433163465307722</v>
+        <v>-0.001027338622224761</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>313.6</v>
+        <v>317.6</v>
       </c>
       <c r="V2">
-        <v>0.57425379967039</v>
+        <v>0.7015683675723438</v>
       </c>
       <c r="W2">
-        <v>-0.3111374678054082</v>
+        <v>-0.3642968142968143</v>
       </c>
       <c r="X2">
-        <v>0.1749729598701272</v>
+        <v>0.2255987954817265</v>
       </c>
       <c r="Y2">
-        <v>-0.4861104276755354</v>
+        <v>-0.5898956097785408</v>
       </c>
       <c r="Z2">
-        <v>1.892714052530049</v>
+        <v>2.178416013925152</v>
       </c>
       <c r="AA2">
-        <v>-0.1794851848975273</v>
+        <v>-0.02655779911163828</v>
       </c>
       <c r="AB2">
-        <v>0.0967888216349128</v>
+        <v>0.08420022415535056</v>
       </c>
       <c r="AC2">
-        <v>-0.2762740065324401</v>
+        <v>-0.1107580232669888</v>
       </c>
       <c r="AD2">
-        <v>792.3</v>
+        <v>956.8000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>792.3</v>
+        <v>956.8000000000001</v>
       </c>
       <c r="AG2">
-        <v>478.6999999999999</v>
+        <v>639.2</v>
       </c>
       <c r="AH2">
-        <v>0.5919754931261206</v>
+        <v>0.6788222774033346</v>
       </c>
       <c r="AI2">
-        <v>0.7081694672863782</v>
+        <v>0.7254530290393509</v>
       </c>
       <c r="AJ2">
-        <v>0.4671155347384855</v>
+        <v>0.5854015935525231</v>
       </c>
       <c r="AK2">
-        <v>0.5945106805762543</v>
+        <v>0.6383701188455009</v>
       </c>
       <c r="AL2">
-        <v>32.22</v>
+        <v>51</v>
       </c>
       <c r="AM2">
-        <v>25.753</v>
+        <v>30.06</v>
       </c>
       <c r="AN2">
-        <v>22.8328530259366</v>
+        <v>8.067453625632378</v>
       </c>
       <c r="AO2">
-        <v>-1.298261949099938</v>
+        <v>0.6254901960784314</v>
       </c>
       <c r="AP2">
-        <v>13.79538904899135</v>
+        <v>5.389544688026982</v>
       </c>
       <c r="AQ2">
-        <v>-1.624276783287384</v>
+        <v>1.061210911510313</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0339</v>
+        <v>-0.00026</v>
       </c>
       <c r="G3">
-        <v>-0.04597009795497509</v>
+        <v>0.06514918897269875</v>
       </c>
       <c r="H3">
-        <v>-0.04597009795497509</v>
+        <v>0.06514918897269875</v>
       </c>
       <c r="I3">
-        <v>-0.002689465543907888</v>
+        <v>0.03604565783325546</v>
       </c>
       <c r="J3">
-        <v>-0.002689465543907888</v>
+        <v>0.02603297510179561</v>
       </c>
       <c r="K3">
-        <v>-30.3</v>
+        <v>31.4</v>
       </c>
       <c r="L3">
-        <v>-0.02603540127169617</v>
+        <v>0.02095988251785595</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +745,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +754,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>290.1</v>
+        <v>287.1</v>
       </c>
       <c r="V3">
-        <v>0.6215984572530534</v>
+        <v>0.7124069478908189</v>
       </c>
       <c r="W3">
-        <v>-0.1157814291173099</v>
+        <v>0.1097902097902098</v>
       </c>
       <c r="X3">
-        <v>0.1555080653055878</v>
+        <v>0.148113746498455</v>
       </c>
       <c r="Y3">
-        <v>-0.2712894944228977</v>
+        <v>-0.03832353670824526</v>
       </c>
       <c r="Z3">
-        <v>2.062012756909993</v>
+        <v>2.437123800227754</v>
       </c>
       <c r="AA3">
-        <v>-0.005545712260807936</v>
+        <v>0.06344558321132261</v>
       </c>
       <c r="AB3">
-        <v>0.09666376952670391</v>
+        <v>0.08276409256214862</v>
       </c>
       <c r="AC3">
-        <v>-0.1022094817875119</v>
+        <v>-0.019318509350826</v>
       </c>
       <c r="AD3">
-        <v>618.8</v>
+        <v>669.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>618.8</v>
+        <v>669.2</v>
       </c>
       <c r="AG3">
-        <v>328.6999999999999</v>
+        <v>382.1</v>
       </c>
       <c r="AH3">
-        <v>0.5700598802395209</v>
+        <v>0.6241372878194367</v>
       </c>
       <c r="AI3">
-        <v>0.6832284420889919</v>
+        <v>0.6653410220719825</v>
       </c>
       <c r="AJ3">
-        <v>0.4132511943676138</v>
+        <v>0.4866895936823335</v>
       </c>
       <c r="AK3">
-        <v>0.5339506172839505</v>
+        <v>0.5316543759565883</v>
       </c>
       <c r="AL3">
-        <v>24.7</v>
+        <v>37.2</v>
       </c>
       <c r="AM3">
-        <v>19.11</v>
+        <v>17.8</v>
       </c>
       <c r="AN3">
-        <v>8.131406044678055</v>
+        <v>4.810927390366643</v>
       </c>
       <c r="AO3">
-        <v>-0.1267206477732793</v>
+        <v>1.451612903225806</v>
       </c>
       <c r="AP3">
-        <v>4.319316688567674</v>
+        <v>2.746944644140906</v>
       </c>
       <c r="AQ3">
-        <v>-0.1637885923600209</v>
+        <v>3.033707865168539</v>
       </c>
     </row>
     <row r="4">
@@ -844,22 +846,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>-0.2193375111906893</v>
+        <v>-0.171259842519685</v>
       </c>
       <c r="H4">
-        <v>-0.2193375111906893</v>
+        <v>-0.171259842519685</v>
       </c>
       <c r="I4">
-        <v>-0.3464637421665175</v>
+        <v>-0.08700787401574804</v>
       </c>
       <c r="J4">
-        <v>-0.3464637421665175</v>
+        <v>-0.08700787401574804</v>
       </c>
       <c r="K4">
-        <v>-39</v>
+        <v>-33.2</v>
       </c>
       <c r="L4">
-        <v>-0.3491495076096687</v>
+        <v>-0.1307086614173228</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -883,73 +885,8845 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>23.5</v>
+        <v>30.5</v>
       </c>
       <c r="V4">
-        <v>0.2959697732997481</v>
+        <v>0.6136820925553319</v>
       </c>
       <c r="W4">
-        <v>-0.5064935064935064</v>
+        <v>-0.8383838383838385</v>
       </c>
       <c r="X4">
-        <v>0.1944378544346667</v>
+        <v>0.3030838444649979</v>
       </c>
       <c r="Y4">
-        <v>-0.7009313609281731</v>
+        <v>-1.141467682848836</v>
       </c>
       <c r="Z4">
-        <v>1.020091324200913</v>
+        <v>1.339662447257384</v>
       </c>
       <c r="AA4">
-        <v>-0.3534246575342466</v>
+        <v>-0.1165611814345992</v>
       </c>
       <c r="AB4">
-        <v>0.09691387374312169</v>
+        <v>0.0856363557485525</v>
       </c>
       <c r="AC4">
-        <v>-0.4503385312773683</v>
+        <v>-0.2021975371831516</v>
       </c>
       <c r="AD4">
-        <v>173.5</v>
+        <v>287.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>173.5</v>
+        <v>287.6</v>
       </c>
       <c r="AG4">
-        <v>150</v>
+        <v>257.1</v>
       </c>
       <c r="AH4">
-        <v>0.6860419137999209</v>
+        <v>0.8526534242514083</v>
       </c>
       <c r="AI4">
-        <v>0.8141717503519474</v>
+        <v>0.9185563717662089</v>
       </c>
       <c r="AJ4">
-        <v>0.6538796861377506</v>
+        <v>0.8380052151238593</v>
       </c>
       <c r="AK4">
-        <v>0.7911392405063291</v>
+        <v>0.9097664543524416</v>
       </c>
       <c r="AL4">
-        <v>7.52</v>
+        <v>13.8</v>
       </c>
       <c r="AM4">
-        <v>6.643</v>
+        <v>12.26</v>
       </c>
       <c r="AN4">
-        <v>-4.190821256038648</v>
+        <v>-14.02926829268293</v>
       </c>
       <c r="AO4">
-        <v>-5.146276595744681</v>
+        <v>-1.601449275362319</v>
       </c>
       <c r="AP4">
-        <v>-3.623188405797102</v>
+        <v>-12.54146341463415</v>
       </c>
       <c r="AQ4">
-        <v>-5.825681168146922</v>
+        <v>-1.802610114192496</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Icelandair Group hf. (ICSE:ICEAIR)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ICSE:ICEAIR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Air Transport</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.17741935483871</v>
+      </c>
+      <c r="F2">
+        <v>4.55031469243476</v>
+      </c>
+      <c r="G2">
+        <v>4.81092739036664</v>
+      </c>
+      <c r="H2">
+        <v>3.08324946081955</v>
+      </c>
+      <c r="I2">
+        <v>0.624137287819437</v>
+      </c>
+      <c r="J2">
+        <v>0.4</v>
+      </c>
+      <c r="K2">
+        <v>403</v>
+      </c>
+      <c r="L2">
+        <v>643.402236287629</v>
+      </c>
+      <c r="M2">
+        <v>785.1</v>
+      </c>
+      <c r="N2">
+        <v>785.1822362876291</v>
+      </c>
+      <c r="O2">
+        <v>669.2</v>
+      </c>
+      <c r="P2">
+        <v>428.88</v>
+      </c>
+      <c r="Q2">
+        <v>0.0827640925621486</v>
+      </c>
+      <c r="R2">
+        <v>0.08275948797025361</v>
+      </c>
+      <c r="S2">
+        <v>0.0434097731713365</v>
+      </c>
+      <c r="T2">
+        <v>0.04072</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.148113746498455</v>
+      </c>
+      <c r="X2">
+        <v>0.110785813283756</v>
+      </c>
+      <c r="Y2">
+        <v>1.87257254596221</v>
+      </c>
+      <c r="Z2">
+        <v>1.23313546531706</v>
+      </c>
+      <c r="AA2">
+        <v>669.2</v>
+      </c>
+      <c r="AB2">
+        <v>0.05426221646417059</v>
+      </c>
+      <c r="AC2">
+        <v>0.1774193548387095</v>
+      </c>
+      <c r="AD2">
+        <v>669.2</v>
+      </c>
+      <c r="AE2">
+        <v>37.2</v>
+      </c>
+      <c r="AF2">
+        <v>132.5</v>
+      </c>
+      <c r="AG2">
+        <v>139.1</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>403</v>
+      </c>
+      <c r="AK2">
+        <v>0.0583762411417202</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.2</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>157</v>
+      </c>
+      <c r="AR2">
+        <v>37.2</v>
+      </c>
+      <c r="AS2">
+        <v>669.2</v>
+      </c>
+      <c r="AT2">
+        <v>287.1</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08574726953288439</v>
+      </c>
+      <c r="C2">
+        <v>1022.312279946672</v>
+      </c>
+      <c r="D2">
+        <v>735.2122799466724</v>
+      </c>
+      <c r="E2">
+        <v>-669.2</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>287.1</v>
+      </c>
+      <c r="H2">
+        <v>403</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K2">
+        <v>132.5</v>
+      </c>
+      <c r="L2">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="O2">
+        <v>19.86666666666667</v>
+      </c>
+      <c r="P2">
+        <v>79.46666666666667</v>
+      </c>
+      <c r="Q2">
+        <v>211.9666666666667</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08574726953288439</v>
+      </c>
+      <c r="T2">
+        <v>0.8042187817285175</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.0856229749938186</v>
+      </c>
+      <c r="C3">
+        <v>1013.541947295096</v>
+      </c>
+      <c r="D3">
+        <v>737.1639472950957</v>
+      </c>
+      <c r="E3">
+        <v>-658.4780000000001</v>
+      </c>
+      <c r="F3">
+        <v>10.722</v>
+      </c>
+      <c r="G3">
+        <v>287.1</v>
+      </c>
+      <c r="H3">
+        <v>403</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K3">
+        <v>132.5</v>
+      </c>
+      <c r="L3">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M3">
+        <v>0.4792734000000001</v>
+      </c>
+      <c r="N3">
+        <v>98.85405993333335</v>
+      </c>
+      <c r="O3">
+        <v>19.77081198666667</v>
+      </c>
+      <c r="P3">
+        <v>79.08324794666667</v>
+      </c>
+      <c r="Q3">
+        <v>211.5832479466667</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08612664140789758</v>
+      </c>
+      <c r="T3">
+        <v>0.8107175193586469</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.2</v>
+      </c>
+      <c r="W3">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>207.2581815167154</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08549868045475284</v>
+      </c>
+      <c r="C4">
+        <v>1004.782003870414</v>
+      </c>
+      <c r="D4">
+        <v>739.1260038704141</v>
+      </c>
+      <c r="E4">
+        <v>-647.7560000000001</v>
+      </c>
+      <c r="F4">
+        <v>21.444</v>
+      </c>
+      <c r="G4">
+        <v>287.1</v>
+      </c>
+      <c r="H4">
+        <v>403</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K4">
+        <v>132.5</v>
+      </c>
+      <c r="L4">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M4">
+        <v>0.9585468000000001</v>
+      </c>
+      <c r="N4">
+        <v>98.37478653333335</v>
+      </c>
+      <c r="O4">
+        <v>19.67495730666667</v>
+      </c>
+      <c r="P4">
+        <v>78.69982922666668</v>
+      </c>
+      <c r="Q4">
+        <v>211.1998292266667</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08651375556607432</v>
+      </c>
+      <c r="T4">
+        <v>0.8173488842873504</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>103.6290907583577</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08537438591568706</v>
+      </c>
+      <c r="C5">
+        <v>996.032532850805</v>
+      </c>
+      <c r="D5">
+        <v>741.098532850805</v>
+      </c>
+      <c r="E5">
+        <v>-637.0340000000001</v>
+      </c>
+      <c r="F5">
+        <v>32.166</v>
+      </c>
+      <c r="G5">
+        <v>287.1</v>
+      </c>
+      <c r="H5">
+        <v>403</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K5">
+        <v>132.5</v>
+      </c>
+      <c r="L5">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M5">
+        <v>1.4378202</v>
+      </c>
+      <c r="N5">
+        <v>97.89551313333334</v>
+      </c>
+      <c r="O5">
+        <v>19.57910262666667</v>
+      </c>
+      <c r="P5">
+        <v>78.31641050666667</v>
+      </c>
+      <c r="Q5">
+        <v>210.8164105066667</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08690885145947121</v>
+      </c>
+      <c r="T5">
+        <v>0.8241169783898415</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.2</v>
+      </c>
+      <c r="W5">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>69.08606050557179</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.0852500913766213</v>
+      </c>
+      <c r="C6">
+        <v>987.2936183047417</v>
+      </c>
+      <c r="D6">
+        <v>743.0816183047416</v>
+      </c>
+      <c r="E6">
+        <v>-626.312</v>
+      </c>
+      <c r="F6">
+        <v>42.88800000000001</v>
+      </c>
+      <c r="G6">
+        <v>287.1</v>
+      </c>
+      <c r="H6">
+        <v>403</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K6">
+        <v>132.5</v>
+      </c>
+      <c r="L6">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M6">
+        <v>1.9170936</v>
+      </c>
+      <c r="N6">
+        <v>97.41623973333334</v>
+      </c>
+      <c r="O6">
+        <v>19.48324794666667</v>
+      </c>
+      <c r="P6">
+        <v>77.93299178666668</v>
+      </c>
+      <c r="Q6">
+        <v>210.4329917866667</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08731217851731386</v>
+      </c>
+      <c r="T6">
+        <v>0.8310260744528014</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.2</v>
+      </c>
+      <c r="W6">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>51.81454537917884</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08512579683755553</v>
+      </c>
+      <c r="C7">
+        <v>978.5653452029384</v>
+      </c>
+      <c r="D7">
+        <v>745.0753452029385</v>
+      </c>
+      <c r="E7">
+        <v>-615.59</v>
+      </c>
+      <c r="F7">
+        <v>53.61000000000001</v>
+      </c>
+      <c r="G7">
+        <v>287.1</v>
+      </c>
+      <c r="H7">
+        <v>403</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K7">
+        <v>132.5</v>
+      </c>
+      <c r="L7">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M7">
+        <v>2.396367000000001</v>
+      </c>
+      <c r="N7">
+        <v>96.93696633333334</v>
+      </c>
+      <c r="O7">
+        <v>19.38739326666667</v>
+      </c>
+      <c r="P7">
+        <v>77.54957306666668</v>
+      </c>
+      <c r="Q7">
+        <v>210.0495730666667</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08772399667111108</v>
+      </c>
+      <c r="T7">
+        <v>0.8380806251697182</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>41.45163630334307</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08500150229848977</v>
+      </c>
+      <c r="C8">
+        <v>969.8477994304861</v>
+      </c>
+      <c r="D8">
+        <v>747.0797994304862</v>
+      </c>
+      <c r="E8">
+        <v>-604.8680000000001</v>
+      </c>
+      <c r="F8">
+        <v>64.33199999999999</v>
+      </c>
+      <c r="G8">
+        <v>287.1</v>
+      </c>
+      <c r="H8">
+        <v>403</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K8">
+        <v>132.5</v>
+      </c>
+      <c r="L8">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M8">
+        <v>2.8756404</v>
+      </c>
+      <c r="N8">
+        <v>96.45769293333335</v>
+      </c>
+      <c r="O8">
+        <v>19.29153858666667</v>
+      </c>
+      <c r="P8">
+        <v>77.16615434666667</v>
+      </c>
+      <c r="Q8">
+        <v>209.6661543466667</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08814457691328699</v>
+      </c>
+      <c r="T8">
+        <v>0.8452852727103992</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>34.5430302527859</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08487720775942399</v>
+      </c>
+      <c r="C9">
+        <v>961.1410677991859</v>
+      </c>
+      <c r="D9">
+        <v>749.0950677991857</v>
+      </c>
+      <c r="E9">
+        <v>-594.1460000000001</v>
+      </c>
+      <c r="F9">
+        <v>75.05400000000002</v>
+      </c>
+      <c r="G9">
+        <v>287.1</v>
+      </c>
+      <c r="H9">
+        <v>403</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K9">
+        <v>132.5</v>
+      </c>
+      <c r="L9">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M9">
+        <v>3.354913800000001</v>
+      </c>
+      <c r="N9">
+        <v>95.97841953333334</v>
+      </c>
+      <c r="O9">
+        <v>19.19568390666667</v>
+      </c>
+      <c r="P9">
+        <v>76.78273562666666</v>
+      </c>
+      <c r="Q9">
+        <v>209.2827356266667</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08857420189185376</v>
+      </c>
+      <c r="T9">
+        <v>0.8526448589078691</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.2</v>
+      </c>
+      <c r="W9">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>29.60831164524505</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08475291322035824</v>
+      </c>
+      <c r="C10">
+        <v>952.4452380600794</v>
+      </c>
+      <c r="D10">
+        <v>751.1212380600795</v>
+      </c>
+      <c r="E10">
+        <v>-583.424</v>
+      </c>
+      <c r="F10">
+        <v>85.77600000000001</v>
+      </c>
+      <c r="G10">
+        <v>287.1</v>
+      </c>
+      <c r="H10">
+        <v>403</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K10">
+        <v>132.5</v>
+      </c>
+      <c r="L10">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M10">
+        <v>3.834187200000001</v>
+      </c>
+      <c r="N10">
+        <v>95.49914613333334</v>
+      </c>
+      <c r="O10">
+        <v>19.09982922666667</v>
+      </c>
+      <c r="P10">
+        <v>76.39931690666667</v>
+      </c>
+      <c r="Q10">
+        <v>208.8993169066667</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08901316654386765</v>
+      </c>
+      <c r="T10">
+        <v>0.8601644361096318</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>25.90727268958942</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08462861868129247</v>
+      </c>
+      <c r="C11">
+        <v>943.7603989161912</v>
+      </c>
+      <c r="D11">
+        <v>753.1583989161911</v>
+      </c>
+      <c r="E11">
+        <v>-572.702</v>
+      </c>
+      <c r="F11">
+        <v>96.498</v>
+      </c>
+      <c r="G11">
+        <v>287.1</v>
+      </c>
+      <c r="H11">
+        <v>403</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K11">
+        <v>132.5</v>
+      </c>
+      <c r="L11">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M11">
+        <v>4.313460600000001</v>
+      </c>
+      <c r="N11">
+        <v>95.01987273333334</v>
+      </c>
+      <c r="O11">
+        <v>19.00397454666667</v>
+      </c>
+      <c r="P11">
+        <v>76.01589818666667</v>
+      </c>
+      <c r="Q11">
+        <v>208.5158981866667</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08946177877065106</v>
+      </c>
+      <c r="T11">
+        <v>0.8678492787444001</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.2</v>
+      </c>
+      <c r="W11">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>23.02868683519059</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08450432414222669</v>
+      </c>
+      <c r="C12">
+        <v>935.0866400354666</v>
+      </c>
+      <c r="D12">
+        <v>755.2066400354666</v>
+      </c>
+      <c r="E12">
+        <v>-561.98</v>
+      </c>
+      <c r="F12">
+        <v>107.22</v>
+      </c>
+      <c r="G12">
+        <v>287.1</v>
+      </c>
+      <c r="H12">
+        <v>403</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K12">
+        <v>132.5</v>
+      </c>
+      <c r="L12">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M12">
+        <v>4.792734000000001</v>
+      </c>
+      <c r="N12">
+        <v>94.54059933333335</v>
+      </c>
+      <c r="O12">
+        <v>18.90811986666667</v>
+      </c>
+      <c r="P12">
+        <v>75.63247946666668</v>
+      </c>
+      <c r="Q12">
+        <v>208.1324794666667</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08992036015802966</v>
+      </c>
+      <c r="T12">
+        <v>0.8757048956599414</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>20.72581815167154</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08438002960316092</v>
+      </c>
+      <c r="C13">
+        <v>926.4240520639332</v>
+      </c>
+      <c r="D13">
+        <v>757.2660520639333</v>
+      </c>
+      <c r="E13">
+        <v>-551.258</v>
+      </c>
+      <c r="F13">
+        <v>117.942</v>
+      </c>
+      <c r="G13">
+        <v>287.1</v>
+      </c>
+      <c r="H13">
+        <v>403</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K13">
+        <v>132.5</v>
+      </c>
+      <c r="L13">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M13">
+        <v>5.272007400000001</v>
+      </c>
+      <c r="N13">
+        <v>94.06132593333334</v>
+      </c>
+      <c r="O13">
+        <v>18.81226518666667</v>
+      </c>
+      <c r="P13">
+        <v>75.24906074666667</v>
+      </c>
+      <c r="Q13">
+        <v>207.7490607466667</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09038924674512464</v>
+      </c>
+      <c r="T13">
+        <v>0.8837370432926854</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.2</v>
+      </c>
+      <c r="W13">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>18.84165286515594</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08425573506409516</v>
+      </c>
+      <c r="C14">
+        <v>917.7727266390714</v>
+      </c>
+      <c r="D14">
+        <v>759.3367266390715</v>
+      </c>
+      <c r="E14">
+        <v>-540.5360000000001</v>
+      </c>
+      <c r="F14">
+        <v>128.664</v>
+      </c>
+      <c r="G14">
+        <v>287.1</v>
+      </c>
+      <c r="H14">
+        <v>403</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K14">
+        <v>132.5</v>
+      </c>
+      <c r="L14">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M14">
+        <v>5.7512808</v>
+      </c>
+      <c r="N14">
+        <v>93.58205253333334</v>
+      </c>
+      <c r="O14">
+        <v>18.71641050666667</v>
+      </c>
+      <c r="P14">
+        <v>74.86564202666668</v>
+      </c>
+      <c r="Q14">
+        <v>207.3656420266667</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09086878984556268</v>
+      </c>
+      <c r="T14">
+        <v>0.8919517397352649</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.2</v>
+      </c>
+      <c r="W14">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>17.27151512639295</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08413144052502937</v>
+      </c>
+      <c r="C15">
+        <v>909.1327564034073</v>
+      </c>
+      <c r="D15">
+        <v>761.4187564034072</v>
+      </c>
+      <c r="E15">
+        <v>-529.8140000000001</v>
+      </c>
+      <c r="F15">
+        <v>139.386</v>
+      </c>
+      <c r="G15">
+        <v>287.1</v>
+      </c>
+      <c r="H15">
+        <v>403</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K15">
+        <v>132.5</v>
+      </c>
+      <c r="L15">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M15">
+        <v>6.230554200000001</v>
+      </c>
+      <c r="N15">
+        <v>93.10277913333334</v>
+      </c>
+      <c r="O15">
+        <v>18.62055582666667</v>
+      </c>
+      <c r="P15">
+        <v>74.48222330666667</v>
+      </c>
+      <c r="Q15">
+        <v>206.9822233066667</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09135935692532113</v>
+      </c>
+      <c r="T15">
+        <v>0.9003552797742252</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.2</v>
+      </c>
+      <c r="W15">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>15.94293703974733</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08400714598596362</v>
+      </c>
+      <c r="C16">
+        <v>900.5042350183272</v>
+      </c>
+      <c r="D16">
+        <v>763.5122350183271</v>
+      </c>
+      <c r="E16">
+        <v>-519.092</v>
+      </c>
+      <c r="F16">
+        <v>150.108</v>
+      </c>
+      <c r="G16">
+        <v>287.1</v>
+      </c>
+      <c r="H16">
+        <v>403</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K16">
+        <v>132.5</v>
+      </c>
+      <c r="L16">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M16">
+        <v>6.709827600000002</v>
+      </c>
+      <c r="N16">
+        <v>92.62350573333335</v>
+      </c>
+      <c r="O16">
+        <v>18.52470114666667</v>
+      </c>
+      <c r="P16">
+        <v>74.09880458666667</v>
+      </c>
+      <c r="Q16">
+        <v>206.5988045866667</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09186133254181816</v>
+      </c>
+      <c r="T16">
+        <v>0.9089542509768825</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.2</v>
+      </c>
+      <c r="W16">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>14.80415582262252</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08388285144689783</v>
+      </c>
+      <c r="C17">
+        <v>891.887257178127</v>
+      </c>
+      <c r="D17">
+        <v>765.6172571781271</v>
+      </c>
+      <c r="E17">
+        <v>-508.37</v>
+      </c>
+      <c r="F17">
+        <v>160.83</v>
+      </c>
+      <c r="G17">
+        <v>287.1</v>
+      </c>
+      <c r="H17">
+        <v>403</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K17">
+        <v>132.5</v>
+      </c>
+      <c r="L17">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M17">
+        <v>7.189101000000001</v>
+      </c>
+      <c r="N17">
+        <v>92.14423233333335</v>
+      </c>
+      <c r="O17">
+        <v>18.42884646666667</v>
+      </c>
+      <c r="P17">
+        <v>73.71538586666668</v>
+      </c>
+      <c r="Q17">
+        <v>206.2153858666667</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09237511934929157</v>
+      </c>
+      <c r="T17">
+        <v>0.9177555509137199</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.2</v>
+      </c>
+      <c r="W17">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>13.81721210111436</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08375855690783207</v>
+      </c>
+      <c r="C18">
+        <v>883.281918624286</v>
+      </c>
+      <c r="D18">
+        <v>767.733918624286</v>
+      </c>
+      <c r="E18">
+        <v>-497.648</v>
+      </c>
+      <c r="F18">
+        <v>171.552</v>
+      </c>
+      <c r="G18">
+        <v>287.1</v>
+      </c>
+      <c r="H18">
+        <v>403</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K18">
+        <v>132.5</v>
+      </c>
+      <c r="L18">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M18">
+        <v>7.668374400000001</v>
+      </c>
+      <c r="N18">
+        <v>91.66495893333334</v>
+      </c>
+      <c r="O18">
+        <v>18.33299178666667</v>
+      </c>
+      <c r="P18">
+        <v>73.33196714666667</v>
+      </c>
+      <c r="Q18">
+        <v>205.8319671466667</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09290113917599056</v>
+      </c>
+      <c r="T18">
+        <v>0.9267664056109581</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.2</v>
+      </c>
+      <c r="W18">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>12.95363634479471</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08378386236876631</v>
+      </c>
+      <c r="C19">
+        <v>872.1280335067662</v>
+      </c>
+      <c r="D19">
+        <v>767.3020335067661</v>
+      </c>
+      <c r="E19">
+        <v>-486.926</v>
+      </c>
+      <c r="F19">
+        <v>182.274</v>
+      </c>
+      <c r="G19">
+        <v>287.1</v>
+      </c>
+      <c r="H19">
+        <v>403</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K19">
+        <v>132.5</v>
+      </c>
+      <c r="L19">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M19">
+        <v>8.348149200000002</v>
+      </c>
+      <c r="N19">
+        <v>90.98518413333335</v>
+      </c>
+      <c r="O19">
+        <v>18.19703682666667</v>
+      </c>
+      <c r="P19">
+        <v>72.78814730666667</v>
+      </c>
+      <c r="Q19">
+        <v>205.2881473066667</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09343983417923651</v>
+      </c>
+      <c r="T19">
+        <v>0.9359943893370456</v>
+      </c>
+      <c r="U19">
+        <v>0.0458</v>
+      </c>
+      <c r="V19">
+        <v>0.2</v>
+      </c>
+      <c r="W19">
+        <v>0.03664</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>11.89884499588643</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.08366836782970054</v>
+      </c>
+      <c r="C20">
+        <v>863.3811264056309</v>
+      </c>
+      <c r="D20">
+        <v>769.2771264056308</v>
+      </c>
+      <c r="E20">
+        <v>-476.2040000000001</v>
+      </c>
+      <c r="F20">
+        <v>192.996</v>
+      </c>
+      <c r="G20">
+        <v>287.1</v>
+      </c>
+      <c r="H20">
+        <v>403</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K20">
+        <v>132.5</v>
+      </c>
+      <c r="L20">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M20">
+        <v>8.839216800000001</v>
+      </c>
+      <c r="N20">
+        <v>90.49411653333334</v>
+      </c>
+      <c r="O20">
+        <v>18.09882330666667</v>
+      </c>
+      <c r="P20">
+        <v>72.39529322666667</v>
+      </c>
+      <c r="Q20">
+        <v>204.8952932266667</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09399166808500066</v>
+      </c>
+      <c r="T20">
+        <v>0.94544744583694</v>
+      </c>
+      <c r="U20">
+        <v>0.0458</v>
+      </c>
+      <c r="V20">
+        <v>0.2</v>
+      </c>
+      <c r="W20">
+        <v>0.03664</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>11.23779805167052</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.08355287329063479</v>
+      </c>
+      <c r="C21">
+        <v>854.6444136195053</v>
+      </c>
+      <c r="D21">
+        <v>771.2624136195052</v>
+      </c>
+      <c r="E21">
+        <v>-465.482</v>
+      </c>
+      <c r="F21">
+        <v>203.718</v>
+      </c>
+      <c r="G21">
+        <v>287.1</v>
+      </c>
+      <c r="H21">
+        <v>403</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K21">
+        <v>132.5</v>
+      </c>
+      <c r="L21">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M21">
+        <v>9.3302844</v>
+      </c>
+      <c r="N21">
+        <v>90.00304893333335</v>
+      </c>
+      <c r="O21">
+        <v>18.00060978666667</v>
+      </c>
+      <c r="P21">
+        <v>72.00243914666667</v>
+      </c>
+      <c r="Q21">
+        <v>204.5024391466667</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.0945571275193022</v>
+      </c>
+      <c r="T21">
+        <v>0.9551339111393011</v>
+      </c>
+      <c r="U21">
+        <v>0.0458</v>
+      </c>
+      <c r="V21">
+        <v>0.2</v>
+      </c>
+      <c r="W21">
+        <v>0.03664</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>10.64633499631944</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.08343737875156901</v>
+      </c>
+      <c r="C22">
+        <v>845.9179742785554</v>
+      </c>
+      <c r="D22">
+        <v>773.2579742785554</v>
+      </c>
+      <c r="E22">
+        <v>-454.76</v>
+      </c>
+      <c r="F22">
+        <v>214.44</v>
+      </c>
+      <c r="G22">
+        <v>287.1</v>
+      </c>
+      <c r="H22">
+        <v>403</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K22">
+        <v>132.5</v>
+      </c>
+      <c r="L22">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M22">
+        <v>9.821352000000001</v>
+      </c>
+      <c r="N22">
+        <v>89.51198133333334</v>
+      </c>
+      <c r="O22">
+        <v>17.90239626666667</v>
+      </c>
+      <c r="P22">
+        <v>71.60958506666667</v>
+      </c>
+      <c r="Q22">
+        <v>204.1095850666667</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09513672343946125</v>
+      </c>
+      <c r="T22">
+        <v>0.9650625380742209</v>
+      </c>
+      <c r="U22">
+        <v>0.0458</v>
+      </c>
+      <c r="V22">
+        <v>0.2</v>
+      </c>
+      <c r="W22">
+        <v>0.03664</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>10.11401824650347</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08369148421250325</v>
+      </c>
+      <c r="C23">
+        <v>830.8189954946727</v>
+      </c>
+      <c r="D23">
+        <v>768.8809954946727</v>
+      </c>
+      <c r="E23">
+        <v>-444.038</v>
+      </c>
+      <c r="F23">
+        <v>225.162</v>
+      </c>
+      <c r="G23">
+        <v>287.1</v>
+      </c>
+      <c r="H23">
+        <v>403</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K23">
+        <v>132.5</v>
+      </c>
+      <c r="L23">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M23">
+        <v>10.807776</v>
+      </c>
+      <c r="N23">
+        <v>88.52555733333334</v>
+      </c>
+      <c r="O23">
+        <v>17.70511146666667</v>
+      </c>
+      <c r="P23">
+        <v>70.82044586666667</v>
+      </c>
+      <c r="Q23">
+        <v>203.3204458666667</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09573099267405473</v>
+      </c>
+      <c r="T23">
+        <v>0.975242522653063</v>
+      </c>
+      <c r="U23">
+        <v>0.048</v>
+      </c>
+      <c r="V23">
+        <v>0.2</v>
+      </c>
+      <c r="W23">
+        <v>0.0384</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>9.190913406544819</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08359358967343747</v>
+      </c>
+      <c r="C24">
+        <v>821.7773531351104</v>
+      </c>
+      <c r="D24">
+        <v>770.5613531351104</v>
+      </c>
+      <c r="E24">
+        <v>-433.316</v>
+      </c>
+      <c r="F24">
+        <v>235.884</v>
+      </c>
+      <c r="G24">
+        <v>287.1</v>
+      </c>
+      <c r="H24">
+        <v>403</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K24">
+        <v>132.5</v>
+      </c>
+      <c r="L24">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M24">
+        <v>11.322432</v>
+      </c>
+      <c r="N24">
+        <v>88.01090133333334</v>
+      </c>
+      <c r="O24">
+        <v>17.60218026666667</v>
+      </c>
+      <c r="P24">
+        <v>70.40872106666667</v>
+      </c>
+      <c r="Q24">
+        <v>202.9087210666667</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09634049958133009</v>
+      </c>
+      <c r="T24">
+        <v>0.9856835324775164</v>
+      </c>
+      <c r="U24">
+        <v>0.048</v>
+      </c>
+      <c r="V24">
+        <v>0.2</v>
+      </c>
+      <c r="W24">
+        <v>0.0384</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>8.773144615338236</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08349569513437172</v>
+      </c>
+      <c r="C25">
+        <v>812.7430715666117</v>
+      </c>
+      <c r="D25">
+        <v>772.2490715666116</v>
+      </c>
+      <c r="E25">
+        <v>-422.5940000000001</v>
+      </c>
+      <c r="F25">
+        <v>246.606</v>
+      </c>
+      <c r="G25">
+        <v>287.1</v>
+      </c>
+      <c r="H25">
+        <v>403</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K25">
+        <v>132.5</v>
+      </c>
+      <c r="L25">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M25">
+        <v>11.837088</v>
+      </c>
+      <c r="N25">
+        <v>87.49624533333335</v>
+      </c>
+      <c r="O25">
+        <v>17.49924906666667</v>
+      </c>
+      <c r="P25">
+        <v>69.99699626666668</v>
+      </c>
+      <c r="Q25">
+        <v>202.4969962666667</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09696583783684637</v>
+      </c>
+      <c r="T25">
+        <v>0.9963957373623451</v>
+      </c>
+      <c r="U25">
+        <v>0.048</v>
+      </c>
+      <c r="V25">
+        <v>0.2</v>
+      </c>
+      <c r="W25">
+        <v>0.0384</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>8.391703545106139</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08339780059530592</v>
+      </c>
+      <c r="C26">
+        <v>803.7161992611591</v>
+      </c>
+      <c r="D26">
+        <v>773.9441992611589</v>
+      </c>
+      <c r="E26">
+        <v>-411.8720000000001</v>
+      </c>
+      <c r="F26">
+        <v>257.328</v>
+      </c>
+      <c r="G26">
+        <v>287.1</v>
+      </c>
+      <c r="H26">
+        <v>403</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K26">
+        <v>132.5</v>
+      </c>
+      <c r="L26">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M26">
+        <v>12.351744</v>
+      </c>
+      <c r="N26">
+        <v>86.98158933333335</v>
+      </c>
+      <c r="O26">
+        <v>17.39631786666667</v>
+      </c>
+      <c r="P26">
+        <v>69.58527146666668</v>
+      </c>
+      <c r="Q26">
+        <v>202.0852714666667</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09760763236224464</v>
+      </c>
+      <c r="T26">
+        <v>1.007389842375722</v>
+      </c>
+      <c r="U26">
+        <v>0.048</v>
+      </c>
+      <c r="V26">
+        <v>0.2</v>
+      </c>
+      <c r="W26">
+        <v>0.0384</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>8.042049230726718</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.08359990605624017</v>
+      </c>
+      <c r="C27">
+        <v>789.5027109323062</v>
+      </c>
+      <c r="D27">
+        <v>770.4527109323062</v>
+      </c>
+      <c r="E27">
+        <v>-401.15</v>
+      </c>
+      <c r="F27">
+        <v>268.05</v>
+      </c>
+      <c r="G27">
+        <v>287.1</v>
+      </c>
+      <c r="H27">
+        <v>403</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K27">
+        <v>132.5</v>
+      </c>
+      <c r="L27">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M27">
+        <v>13.268475</v>
+      </c>
+      <c r="N27">
+        <v>86.06485833333335</v>
+      </c>
+      <c r="O27">
+        <v>17.21297166666667</v>
+      </c>
+      <c r="P27">
+        <v>68.85188666666667</v>
+      </c>
+      <c r="Q27">
+        <v>201.3518866666667</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09826654140832021</v>
+      </c>
+      <c r="T27">
+        <v>1.018677123522789</v>
+      </c>
+      <c r="U27">
+        <v>0.0495</v>
+      </c>
+      <c r="V27">
+        <v>0.2</v>
+      </c>
+      <c r="W27">
+        <v>0.0396</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>7.486416738421962</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.08351401151717439</v>
+      </c>
+      <c r="C28">
+        <v>780.2607320315559</v>
+      </c>
+      <c r="D28">
+        <v>771.9327320315559</v>
+      </c>
+      <c r="E28">
+        <v>-390.428</v>
+      </c>
+      <c r="F28">
+        <v>278.772</v>
+      </c>
+      <c r="G28">
+        <v>287.1</v>
+      </c>
+      <c r="H28">
+        <v>403</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K28">
+        <v>132.5</v>
+      </c>
+      <c r="L28">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M28">
+        <v>13.799214</v>
+      </c>
+      <c r="N28">
+        <v>85.53411933333334</v>
+      </c>
+      <c r="O28">
+        <v>17.10682386666667</v>
+      </c>
+      <c r="P28">
+        <v>68.42729546666666</v>
+      </c>
+      <c r="Q28">
+        <v>200.9272954666667</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09894325880699242</v>
+      </c>
+      <c r="T28">
+        <v>1.030269466322479</v>
+      </c>
+      <c r="U28">
+        <v>0.0495</v>
+      </c>
+      <c r="V28">
+        <v>0.2</v>
+      </c>
+      <c r="W28">
+        <v>0.0396</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>7.198477633098038</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08342811697810863</v>
+      </c>
+      <c r="C29">
+        <v>771.0244502445861</v>
+      </c>
+      <c r="D29">
+        <v>773.4184502445861</v>
+      </c>
+      <c r="E29">
+        <v>-379.706</v>
+      </c>
+      <c r="F29">
+        <v>289.494</v>
+      </c>
+      <c r="G29">
+        <v>287.1</v>
+      </c>
+      <c r="H29">
+        <v>403</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K29">
+        <v>132.5</v>
+      </c>
+      <c r="L29">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M29">
+        <v>14.329953</v>
+      </c>
+      <c r="N29">
+        <v>85.00338033333334</v>
+      </c>
+      <c r="O29">
+        <v>17.00067606666667</v>
+      </c>
+      <c r="P29">
+        <v>68.00270426666667</v>
+      </c>
+      <c r="Q29">
+        <v>200.5027042666667</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09963851640836797</v>
+      </c>
+      <c r="T29">
+        <v>1.042179407555038</v>
+      </c>
+      <c r="U29">
+        <v>0.0495</v>
+      </c>
+      <c r="V29">
+        <v>0.2</v>
+      </c>
+      <c r="W29">
+        <v>0.0396</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>6.931867350390704</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.08334222243904285</v>
+      </c>
+      <c r="C30">
+        <v>761.7938985300784</v>
+      </c>
+      <c r="D30">
+        <v>774.9098985300785</v>
+      </c>
+      <c r="E30">
+        <v>-368.984</v>
+      </c>
+      <c r="F30">
+        <v>300.2160000000001</v>
+      </c>
+      <c r="G30">
+        <v>287.1</v>
+      </c>
+      <c r="H30">
+        <v>403</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K30">
+        <v>132.5</v>
+      </c>
+      <c r="L30">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M30">
+        <v>14.860692</v>
+      </c>
+      <c r="N30">
+        <v>84.47264133333334</v>
+      </c>
+      <c r="O30">
+        <v>16.89452826666667</v>
+      </c>
+      <c r="P30">
+        <v>67.57811306666667</v>
+      </c>
+      <c r="Q30">
+        <v>200.0781130666667</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1003530867208929</v>
+      </c>
+      <c r="T30">
+        <v>1.054420180488501</v>
+      </c>
+      <c r="U30">
+        <v>0.0495</v>
+      </c>
+      <c r="V30">
+        <v>0.2</v>
+      </c>
+      <c r="W30">
+        <v>0.0396</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>6.684300659305322</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.08325632789997707</v>
+      </c>
+      <c r="C31">
+        <v>752.5691101014323</v>
+      </c>
+      <c r="D31">
+        <v>776.4071101014324</v>
+      </c>
+      <c r="E31">
+        <v>-358.2620000000001</v>
+      </c>
+      <c r="F31">
+        <v>310.938</v>
+      </c>
+      <c r="G31">
+        <v>287.1</v>
+      </c>
+      <c r="H31">
+        <v>403</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K31">
+        <v>132.5</v>
+      </c>
+      <c r="L31">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M31">
+        <v>15.391431</v>
+      </c>
+      <c r="N31">
+        <v>83.94190233333335</v>
+      </c>
+      <c r="O31">
+        <v>16.78838046666667</v>
+      </c>
+      <c r="P31">
+        <v>67.15352186666668</v>
+      </c>
+      <c r="Q31">
+        <v>199.6535218666667</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1010877857746156</v>
+      </c>
+      <c r="T31">
+        <v>1.067005763927132</v>
+      </c>
+      <c r="U31">
+        <v>0.0495</v>
+      </c>
+      <c r="V31">
+        <v>0.2</v>
+      </c>
+      <c r="W31">
+        <v>0.0396</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>6.453807533122381</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.08317043336091132</v>
+      </c>
+      <c r="C32">
+        <v>743.3501184292322</v>
+      </c>
+      <c r="D32">
+        <v>777.9101184292323</v>
+      </c>
+      <c r="E32">
+        <v>-347.54</v>
+      </c>
+      <c r="F32">
+        <v>321.66</v>
+      </c>
+      <c r="G32">
+        <v>287.1</v>
+      </c>
+      <c r="H32">
+        <v>403</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K32">
+        <v>132.5</v>
+      </c>
+      <c r="L32">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M32">
+        <v>15.92217</v>
+      </c>
+      <c r="N32">
+        <v>83.41116333333335</v>
+      </c>
+      <c r="O32">
+        <v>16.68223266666667</v>
+      </c>
+      <c r="P32">
+        <v>66.72893066666668</v>
+      </c>
+      <c r="Q32">
+        <v>199.2289306666667</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1018434762298733</v>
+      </c>
+      <c r="T32">
+        <v>1.079950935464009</v>
+      </c>
+      <c r="U32">
+        <v>0.0495</v>
+      </c>
+      <c r="V32">
+        <v>0.2</v>
+      </c>
+      <c r="W32">
+        <v>0.0396</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>6.238680615351635</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.08343173882184554</v>
+      </c>
+      <c r="C33">
+        <v>728.0736877163054</v>
+      </c>
+      <c r="D33">
+        <v>773.3556877163053</v>
+      </c>
+      <c r="E33">
+        <v>-336.818</v>
+      </c>
+      <c r="F33">
+        <v>332.382</v>
+      </c>
+      <c r="G33">
+        <v>287.1</v>
+      </c>
+      <c r="H33">
+        <v>403</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K33">
+        <v>132.5</v>
+      </c>
+      <c r="L33">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M33">
+        <v>16.9182438</v>
+      </c>
+      <c r="N33">
+        <v>82.41508953333334</v>
+      </c>
+      <c r="O33">
+        <v>16.48301790666667</v>
+      </c>
+      <c r="P33">
+        <v>65.93207162666667</v>
+      </c>
+      <c r="Q33">
+        <v>198.4320716266667</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1026210707562979</v>
+      </c>
+      <c r="T33">
+        <v>1.093271329364274</v>
+      </c>
+      <c r="U33">
+        <v>0.0509</v>
+      </c>
+      <c r="V33">
+        <v>0.2</v>
+      </c>
+      <c r="W33">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>5.871373796690017</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.08335704428277976</v>
+      </c>
+      <c r="C34">
+        <v>718.6481257444038</v>
+      </c>
+      <c r="D34">
+        <v>774.6521257444039</v>
+      </c>
+      <c r="E34">
+        <v>-326.096</v>
+      </c>
+      <c r="F34">
+        <v>343.104</v>
+      </c>
+      <c r="G34">
+        <v>287.1</v>
+      </c>
+      <c r="H34">
+        <v>403</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K34">
+        <v>132.5</v>
+      </c>
+      <c r="L34">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M34">
+        <v>17.4639936</v>
+      </c>
+      <c r="N34">
+        <v>81.86933973333333</v>
+      </c>
+      <c r="O34">
+        <v>16.37386794666667</v>
+      </c>
+      <c r="P34">
+        <v>65.49547178666667</v>
+      </c>
+      <c r="Q34">
+        <v>197.9954717866667</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1034215357099703</v>
+      </c>
+      <c r="T34">
+        <v>1.106983499555724</v>
+      </c>
+      <c r="U34">
+        <v>0.0509</v>
+      </c>
+      <c r="V34">
+        <v>0.2</v>
+      </c>
+      <c r="W34">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>5.687893365543453</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.08328234974371401</v>
+      </c>
+      <c r="C35">
+        <v>709.2269177169987</v>
+      </c>
+      <c r="D35">
+        <v>775.9529177169987</v>
+      </c>
+      <c r="E35">
+        <v>-315.374</v>
+      </c>
+      <c r="F35">
+        <v>353.826</v>
+      </c>
+      <c r="G35">
+        <v>287.1</v>
+      </c>
+      <c r="H35">
+        <v>403</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K35">
+        <v>132.5</v>
+      </c>
+      <c r="L35">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M35">
+        <v>18.0097434</v>
+      </c>
+      <c r="N35">
+        <v>81.32358993333334</v>
+      </c>
+      <c r="O35">
+        <v>16.26471798666667</v>
+      </c>
+      <c r="P35">
+        <v>65.05887194666667</v>
+      </c>
+      <c r="Q35">
+        <v>197.5588719466667</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1042458951398717</v>
+      </c>
+      <c r="T35">
+        <v>1.121104988260351</v>
+      </c>
+      <c r="U35">
+        <v>0.0509</v>
+      </c>
+      <c r="V35">
+        <v>0.2</v>
+      </c>
+      <c r="W35">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>5.515532960526985</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.08320765520464823</v>
+      </c>
+      <c r="C36">
+        <v>699.8100856043486</v>
+      </c>
+      <c r="D36">
+        <v>777.2580856043487</v>
+      </c>
+      <c r="E36">
+        <v>-304.652</v>
+      </c>
+      <c r="F36">
+        <v>364.5480000000001</v>
+      </c>
+      <c r="G36">
+        <v>287.1</v>
+      </c>
+      <c r="H36">
+        <v>403</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K36">
+        <v>132.5</v>
+      </c>
+      <c r="L36">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M36">
+        <v>18.5554932</v>
+      </c>
+      <c r="N36">
+        <v>80.77784013333334</v>
+      </c>
+      <c r="O36">
+        <v>16.15556802666667</v>
+      </c>
+      <c r="P36">
+        <v>64.62227210666667</v>
+      </c>
+      <c r="Q36">
+        <v>197.1222721066667</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1050952351585579</v>
+      </c>
+      <c r="T36">
+        <v>1.135654400865119</v>
+      </c>
+      <c r="U36">
+        <v>0.0509</v>
+      </c>
+      <c r="V36">
+        <v>0.2</v>
+      </c>
+      <c r="W36">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>5.353311402864426</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.08313296066558247</v>
+      </c>
+      <c r="C37">
+        <v>690.3976515247775</v>
+      </c>
+      <c r="D37">
+        <v>778.5676515247775</v>
+      </c>
+      <c r="E37">
+        <v>-293.93</v>
+      </c>
+      <c r="F37">
+        <v>375.27</v>
+      </c>
+      <c r="G37">
+        <v>287.1</v>
+      </c>
+      <c r="H37">
+        <v>403</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K37">
+        <v>132.5</v>
+      </c>
+      <c r="L37">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M37">
+        <v>19.101243</v>
+      </c>
+      <c r="N37">
+        <v>80.23209033333333</v>
+      </c>
+      <c r="O37">
+        <v>16.04641806666667</v>
+      </c>
+      <c r="P37">
+        <v>64.18567226666667</v>
+      </c>
+      <c r="Q37">
+        <v>196.6856722666667</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1059707087162807</v>
+      </c>
+      <c r="T37">
+        <v>1.150651487703879</v>
+      </c>
+      <c r="U37">
+        <v>0.0509</v>
+      </c>
+      <c r="V37">
+        <v>0.2</v>
+      </c>
+      <c r="W37">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>5.200359648496871</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.08305826612651671</v>
+      </c>
+      <c r="C38">
+        <v>680.9896377459258</v>
+      </c>
+      <c r="D38">
+        <v>779.8816377459258</v>
+      </c>
+      <c r="E38">
+        <v>-283.208</v>
+      </c>
+      <c r="F38">
+        <v>385.992</v>
+      </c>
+      <c r="G38">
+        <v>287.1</v>
+      </c>
+      <c r="H38">
+        <v>403</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K38">
+        <v>132.5</v>
+      </c>
+      <c r="L38">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M38">
+        <v>19.6469928</v>
+      </c>
+      <c r="N38">
+        <v>79.68634053333335</v>
+      </c>
+      <c r="O38">
+        <v>15.93726810666667</v>
+      </c>
+      <c r="P38">
+        <v>63.74907242666668</v>
+      </c>
+      <c r="Q38">
+        <v>196.2490724266667</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1068735408226824</v>
+      </c>
+      <c r="T38">
+        <v>1.16611723350635</v>
+      </c>
+      <c r="U38">
+        <v>0.0509</v>
+      </c>
+      <c r="V38">
+        <v>0.2</v>
+      </c>
+      <c r="W38">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>5.055905213816404</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.08298357158745095</v>
+      </c>
+      <c r="C39">
+        <v>671.5860666860121</v>
+      </c>
+      <c r="D39">
+        <v>781.2000666860122</v>
+      </c>
+      <c r="E39">
+        <v>-272.486</v>
+      </c>
+      <c r="F39">
+        <v>396.714</v>
+      </c>
+      <c r="G39">
+        <v>287.1</v>
+      </c>
+      <c r="H39">
+        <v>403</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K39">
+        <v>132.5</v>
+      </c>
+      <c r="L39">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M39">
+        <v>20.1927426</v>
+      </c>
+      <c r="N39">
+        <v>79.14059073333334</v>
+      </c>
+      <c r="O39">
+        <v>15.82811814666667</v>
+      </c>
+      <c r="P39">
+        <v>63.31247258666667</v>
+      </c>
+      <c r="Q39">
+        <v>195.8124725866667</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1078050342657951</v>
+      </c>
+      <c r="T39">
+        <v>1.182073955366043</v>
+      </c>
+      <c r="U39">
+        <v>0.0509</v>
+      </c>
+      <c r="V39">
+        <v>0.2</v>
+      </c>
+      <c r="W39">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>4.919259126956501</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.08290887704838516</v>
+      </c>
+      <c r="C40">
+        <v>662.1869609151096</v>
+      </c>
+      <c r="D40">
+        <v>782.5229609151096</v>
+      </c>
+      <c r="E40">
+        <v>-261.764</v>
+      </c>
+      <c r="F40">
+        <v>407.436</v>
+      </c>
+      <c r="G40">
+        <v>287.1</v>
+      </c>
+      <c r="H40">
+        <v>403</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K40">
+        <v>132.5</v>
+      </c>
+      <c r="L40">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M40">
+        <v>20.7384924</v>
+      </c>
+      <c r="N40">
+        <v>78.59484093333334</v>
+      </c>
+      <c r="O40">
+        <v>15.71896818666667</v>
+      </c>
+      <c r="P40">
+        <v>62.87587274666667</v>
+      </c>
+      <c r="Q40">
+        <v>195.3758727466667</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1087665758844922</v>
+      </c>
+      <c r="T40">
+        <v>1.198545410188952</v>
+      </c>
+      <c r="U40">
+        <v>0.0509</v>
+      </c>
+      <c r="V40">
+        <v>0.2</v>
+      </c>
+      <c r="W40">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>4.789804939405014</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.0828341825093194</v>
+      </c>
+      <c r="C41">
+        <v>652.7923431564299</v>
+      </c>
+      <c r="D41">
+        <v>783.85034315643</v>
+      </c>
+      <c r="E41">
+        <v>-251.042</v>
+      </c>
+      <c r="F41">
+        <v>418.158</v>
+      </c>
+      <c r="G41">
+        <v>287.1</v>
+      </c>
+      <c r="H41">
+        <v>403</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K41">
+        <v>132.5</v>
+      </c>
+      <c r="L41">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M41">
+        <v>21.2842422</v>
+      </c>
+      <c r="N41">
+        <v>78.04909113333335</v>
+      </c>
+      <c r="O41">
+        <v>15.60981822666667</v>
+      </c>
+      <c r="P41">
+        <v>62.43927290666668</v>
+      </c>
+      <c r="Q41">
+        <v>194.9392729066667</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1097596434579007</v>
+      </c>
+      <c r="T41">
+        <v>1.215556912710972</v>
+      </c>
+      <c r="U41">
+        <v>0.0509</v>
+      </c>
+      <c r="V41">
+        <v>0.2</v>
+      </c>
+      <c r="W41">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>4.666989428138219</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.08275948797025362</v>
+      </c>
+      <c r="C42">
+        <v>643.4022362876294</v>
+      </c>
+      <c r="D42">
+        <v>785.1822362876294</v>
+      </c>
+      <c r="E42">
+        <v>-240.32</v>
+      </c>
+      <c r="F42">
+        <v>428.8800000000001</v>
+      </c>
+      <c r="G42">
+        <v>287.1</v>
+      </c>
+      <c r="H42">
+        <v>403</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K42">
+        <v>132.5</v>
+      </c>
+      <c r="L42">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M42">
+        <v>21.829992</v>
+      </c>
+      <c r="N42">
+        <v>77.50334133333334</v>
+      </c>
+      <c r="O42">
+        <v>15.50066826666667</v>
+      </c>
+      <c r="P42">
+        <v>62.00267306666667</v>
+      </c>
+      <c r="Q42">
+        <v>194.5026730666667</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.110785813283756</v>
+      </c>
+      <c r="T42">
+        <v>1.23313546531706</v>
+      </c>
+      <c r="U42">
+        <v>0.0509</v>
+      </c>
+      <c r="V42">
+        <v>0.2</v>
+      </c>
+      <c r="W42">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>4.550314692434762</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.08353759343118787</v>
+      </c>
+      <c r="C43">
+        <v>619.0238337181952</v>
+      </c>
+      <c r="D43">
+        <v>771.5258337181954</v>
+      </c>
+      <c r="E43">
+        <v>-229.598</v>
+      </c>
+      <c r="F43">
+        <v>439.602</v>
+      </c>
+      <c r="G43">
+        <v>287.1</v>
+      </c>
+      <c r="H43">
+        <v>403</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K43">
+        <v>132.5</v>
+      </c>
+      <c r="L43">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M43">
+        <v>23.518707</v>
+      </c>
+      <c r="N43">
+        <v>75.81462633333334</v>
+      </c>
+      <c r="O43">
+        <v>15.16292526666667</v>
+      </c>
+      <c r="P43">
+        <v>60.65170106666667</v>
+      </c>
+      <c r="Q43">
+        <v>193.1517010666667</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1118467685274371</v>
+      </c>
+      <c r="T43">
+        <v>1.251309901062337</v>
+      </c>
+      <c r="U43">
+        <v>0.0535</v>
+      </c>
+      <c r="V43">
+        <v>0.2</v>
+      </c>
+      <c r="W43">
+        <v>0.0428</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>4.223588198676625</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.08348369889212209</v>
+      </c>
+      <c r="C44">
+        <v>609.2323974409069</v>
+      </c>
+      <c r="D44">
+        <v>772.456397440907</v>
+      </c>
+      <c r="E44">
+        <v>-218.876</v>
+      </c>
+      <c r="F44">
+        <v>450.324</v>
+      </c>
+      <c r="G44">
+        <v>287.1</v>
+      </c>
+      <c r="H44">
+        <v>403</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K44">
+        <v>132.5</v>
+      </c>
+      <c r="L44">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M44">
+        <v>24.092334</v>
+      </c>
+      <c r="N44">
+        <v>75.24099933333335</v>
+      </c>
+      <c r="O44">
+        <v>15.04819986666667</v>
+      </c>
+      <c r="P44">
+        <v>60.19279946666668</v>
+      </c>
+      <c r="Q44">
+        <v>192.6927994666667</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1129443084346932</v>
+      </c>
+      <c r="T44">
+        <v>1.270111041488486</v>
+      </c>
+      <c r="U44">
+        <v>0.0535</v>
+      </c>
+      <c r="V44">
+        <v>0.2</v>
+      </c>
+      <c r="W44">
+        <v>0.0428</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>4.123026574898611</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.08342980435305633</v>
+      </c>
+      <c r="C45">
+        <v>599.4432086439126</v>
+      </c>
+      <c r="D45">
+        <v>773.3892086439126</v>
+      </c>
+      <c r="E45">
+        <v>-208.1540000000001</v>
+      </c>
+      <c r="F45">
+        <v>461.046</v>
+      </c>
+      <c r="G45">
+        <v>287.1</v>
+      </c>
+      <c r="H45">
+        <v>403</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K45">
+        <v>132.5</v>
+      </c>
+      <c r="L45">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M45">
+        <v>24.665961</v>
+      </c>
+      <c r="N45">
+        <v>74.66737233333335</v>
+      </c>
+      <c r="O45">
+        <v>14.93347446666667</v>
+      </c>
+      <c r="P45">
+        <v>59.73389786666668</v>
+      </c>
+      <c r="Q45">
+        <v>192.2338978666667</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1140803585141339</v>
+      </c>
+      <c r="T45">
+        <v>1.289571871052395</v>
+      </c>
+      <c r="U45">
+        <v>0.0535</v>
+      </c>
+      <c r="V45">
+        <v>0.2</v>
+      </c>
+      <c r="W45">
+        <v>0.0428</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>4.02714223594748</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.08432630981399056</v>
+      </c>
+      <c r="C46">
+        <v>573.4916051067553</v>
+      </c>
+      <c r="D46">
+        <v>758.1596051067553</v>
+      </c>
+      <c r="E46">
+        <v>-197.432</v>
+      </c>
+      <c r="F46">
+        <v>471.768</v>
+      </c>
+      <c r="G46">
+        <v>287.1</v>
+      </c>
+      <c r="H46">
+        <v>403</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K46">
+        <v>132.5</v>
+      </c>
+      <c r="L46">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M46">
+        <v>26.5133616</v>
+      </c>
+      <c r="N46">
+        <v>72.81997173333335</v>
+      </c>
+      <c r="O46">
+        <v>14.56399434666667</v>
+      </c>
+      <c r="P46">
+        <v>58.25597738666668</v>
+      </c>
+      <c r="Q46">
+        <v>190.7559773866667</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1152569818106974</v>
+      </c>
+      <c r="T46">
+        <v>1.309727730243585</v>
+      </c>
+      <c r="U46">
+        <v>0.0562</v>
+      </c>
+      <c r="V46">
+        <v>0.2</v>
+      </c>
+      <c r="W46">
+        <v>0.04496</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>3.746538625767218</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.08429401527492479</v>
+      </c>
+      <c r="C47">
+        <v>563.3077949068256</v>
+      </c>
+      <c r="D47">
+        <v>758.6977949068256</v>
+      </c>
+      <c r="E47">
+        <v>-186.71</v>
+      </c>
+      <c r="F47">
+        <v>482.49</v>
+      </c>
+      <c r="G47">
+        <v>287.1</v>
+      </c>
+      <c r="H47">
+        <v>403</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K47">
+        <v>132.5</v>
+      </c>
+      <c r="L47">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M47">
+        <v>27.115938</v>
+      </c>
+      <c r="N47">
+        <v>72.21739533333334</v>
+      </c>
+      <c r="O47">
+        <v>14.44347906666667</v>
+      </c>
+      <c r="P47">
+        <v>57.77391626666667</v>
+      </c>
+      <c r="Q47">
+        <v>190.2739162666667</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1164763914089541</v>
+      </c>
+      <c r="T47">
+        <v>1.330616529769002</v>
+      </c>
+      <c r="U47">
+        <v>0.0562</v>
+      </c>
+      <c r="V47">
+        <v>0.2</v>
+      </c>
+      <c r="W47">
+        <v>0.04496</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>3.66328221186128</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.08426172073585902</v>
+      </c>
+      <c r="C48">
+        <v>553.1247493322221</v>
+      </c>
+      <c r="D48">
+        <v>759.2367493322221</v>
+      </c>
+      <c r="E48">
+        <v>-175.988</v>
+      </c>
+      <c r="F48">
+        <v>493.212</v>
+      </c>
+      <c r="G48">
+        <v>287.1</v>
+      </c>
+      <c r="H48">
+        <v>403</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K48">
+        <v>132.5</v>
+      </c>
+      <c r="L48">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M48">
+        <v>27.7185144</v>
+      </c>
+      <c r="N48">
+        <v>71.61481893333334</v>
+      </c>
+      <c r="O48">
+        <v>14.32296378666667</v>
+      </c>
+      <c r="P48">
+        <v>57.29185514666667</v>
+      </c>
+      <c r="Q48">
+        <v>189.7918551466667</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1177409643256648</v>
+      </c>
+      <c r="T48">
+        <v>1.3522789885361</v>
+      </c>
+      <c r="U48">
+        <v>0.0562</v>
+      </c>
+      <c r="V48">
+        <v>0.2</v>
+      </c>
+      <c r="W48">
+        <v>0.04496</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>3.583645642038209</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.08422942619679324</v>
+      </c>
+      <c r="C49">
+        <v>542.9424700135989</v>
+      </c>
+      <c r="D49">
+        <v>759.7764700135988</v>
+      </c>
+      <c r="E49">
+        <v>-165.266</v>
+      </c>
+      <c r="F49">
+        <v>503.934</v>
+      </c>
+      <c r="G49">
+        <v>287.1</v>
+      </c>
+      <c r="H49">
+        <v>403</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K49">
+        <v>132.5</v>
+      </c>
+      <c r="L49">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M49">
+        <v>28.3210908</v>
+      </c>
+      <c r="N49">
+        <v>71.01224253333334</v>
+      </c>
+      <c r="O49">
+        <v>14.20244850666667</v>
+      </c>
+      <c r="P49">
+        <v>56.80979402666667</v>
+      </c>
+      <c r="Q49">
+        <v>189.3097940266667</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1190532569750816</v>
+      </c>
+      <c r="T49">
+        <v>1.374758898577428</v>
+      </c>
+      <c r="U49">
+        <v>0.0562</v>
+      </c>
+      <c r="V49">
+        <v>0.2</v>
+      </c>
+      <c r="W49">
+        <v>0.04496</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>3.507397862420374</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.08600193165772749</v>
+      </c>
+      <c r="C50">
+        <v>503.6896897066879</v>
+      </c>
+      <c r="D50">
+        <v>731.2456897066878</v>
+      </c>
+      <c r="E50">
+        <v>-154.5440000000001</v>
+      </c>
+      <c r="F50">
+        <v>514.6559999999999</v>
+      </c>
+      <c r="G50">
+        <v>287.1</v>
+      </c>
+      <c r="H50">
+        <v>403</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K50">
+        <v>132.5</v>
+      </c>
+      <c r="L50">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M50">
+        <v>31.3425504</v>
+      </c>
+      <c r="N50">
+        <v>67.99078293333335</v>
+      </c>
+      <c r="O50">
+        <v>13.59815658666667</v>
+      </c>
+      <c r="P50">
+        <v>54.39262634666668</v>
+      </c>
+      <c r="Q50">
+        <v>186.8926263466667</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1204160224187067</v>
+      </c>
+      <c r="T50">
+        <v>1.398103420543423</v>
+      </c>
+      <c r="U50">
+        <v>0.0609</v>
+      </c>
+      <c r="V50">
+        <v>0.2</v>
+      </c>
+      <c r="W50">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>3.169280485015455</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.08600723711866172</v>
+      </c>
+      <c r="C51">
+        <v>492.885507488942</v>
+      </c>
+      <c r="D51">
+        <v>731.1635074889421</v>
+      </c>
+      <c r="E51">
+        <v>-143.822</v>
+      </c>
+      <c r="F51">
+        <v>525.378</v>
+      </c>
+      <c r="G51">
+        <v>287.1</v>
+      </c>
+      <c r="H51">
+        <v>403</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K51">
+        <v>132.5</v>
+      </c>
+      <c r="L51">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M51">
+        <v>31.9955202</v>
+      </c>
+      <c r="N51">
+        <v>67.33781313333334</v>
+      </c>
+      <c r="O51">
+        <v>13.46756262666667</v>
+      </c>
+      <c r="P51">
+        <v>53.87025050666667</v>
+      </c>
+      <c r="Q51">
+        <v>186.3702505066667</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1218322296444347</v>
+      </c>
+      <c r="T51">
+        <v>1.422363413959064</v>
+      </c>
+      <c r="U51">
+        <v>0.0609</v>
+      </c>
+      <c r="V51">
+        <v>0.2</v>
+      </c>
+      <c r="W51">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>3.104601291443711</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.08601254257959595</v>
+      </c>
+      <c r="C52">
+        <v>482.0813437414806</v>
+      </c>
+      <c r="D52">
+        <v>731.0813437414806</v>
+      </c>
+      <c r="E52">
+        <v>-133.1</v>
+      </c>
+      <c r="F52">
+        <v>536.1</v>
+      </c>
+      <c r="G52">
+        <v>287.1</v>
+      </c>
+      <c r="H52">
+        <v>403</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K52">
+        <v>132.5</v>
+      </c>
+      <c r="L52">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M52">
+        <v>32.64849</v>
+      </c>
+      <c r="N52">
+        <v>66.68484333333333</v>
+      </c>
+      <c r="O52">
+        <v>13.33696866666667</v>
+      </c>
+      <c r="P52">
+        <v>53.34787466666667</v>
+      </c>
+      <c r="Q52">
+        <v>185.8478746666667</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1233050851591919</v>
+      </c>
+      <c r="T52">
+        <v>1.447593807111331</v>
+      </c>
+      <c r="U52">
+        <v>0.0609</v>
+      </c>
+      <c r="V52">
+        <v>0.2</v>
+      </c>
+      <c r="W52">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>3.042509265614836</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.08981224804053017</v>
+      </c>
+      <c r="C53">
+        <v>416.9039162528794</v>
+      </c>
+      <c r="D53">
+        <v>676.6259162528794</v>
+      </c>
+      <c r="E53">
+        <v>-122.378</v>
+      </c>
+      <c r="F53">
+        <v>546.822</v>
+      </c>
+      <c r="G53">
+        <v>287.1</v>
+      </c>
+      <c r="H53">
+        <v>403</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K53">
+        <v>132.5</v>
+      </c>
+      <c r="L53">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M53">
+        <v>38.3869044</v>
+      </c>
+      <c r="N53">
+        <v>60.94642893333334</v>
+      </c>
+      <c r="O53">
+        <v>12.18928578666667</v>
+      </c>
+      <c r="P53">
+        <v>48.75714314666668</v>
+      </c>
+      <c r="Q53">
+        <v>181.2571431466667</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1248380572255718</v>
+      </c>
+      <c r="T53">
+        <v>1.473854012228998</v>
+      </c>
+      <c r="U53">
+        <v>0.0702</v>
+      </c>
+      <c r="V53">
+        <v>0.2</v>
+      </c>
+      <c r="W53">
+        <v>0.05616</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>2.587688038041779</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.08989195350146439</v>
+      </c>
+      <c r="C54">
+        <v>405.1263531585179</v>
+      </c>
+      <c r="D54">
+        <v>675.5703531585179</v>
+      </c>
+      <c r="E54">
+        <v>-111.6559999999999</v>
+      </c>
+      <c r="F54">
+        <v>557.5440000000001</v>
+      </c>
+      <c r="G54">
+        <v>287.1</v>
+      </c>
+      <c r="H54">
+        <v>403</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K54">
+        <v>132.5</v>
+      </c>
+      <c r="L54">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M54">
+        <v>39.13958880000001</v>
+      </c>
+      <c r="N54">
+        <v>60.19374453333334</v>
+      </c>
+      <c r="O54">
+        <v>12.03874890666667</v>
+      </c>
+      <c r="P54">
+        <v>48.15499562666667</v>
+      </c>
+      <c r="Q54">
+        <v>180.6549956266667</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1264349031280508</v>
+      </c>
+      <c r="T54">
+        <v>1.501208392559899</v>
+      </c>
+      <c r="U54">
+        <v>0.0702</v>
+      </c>
+      <c r="V54">
+        <v>0.2</v>
+      </c>
+      <c r="W54">
+        <v>0.05616</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>2.537924806540976</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.09196445896239863</v>
+      </c>
+      <c r="C55">
+        <v>368.0686530781962</v>
+      </c>
+      <c r="D55">
+        <v>649.2346530781963</v>
+      </c>
+      <c r="E55">
+        <v>-100.934</v>
+      </c>
+      <c r="F55">
+        <v>568.2660000000001</v>
+      </c>
+      <c r="G55">
+        <v>287.1</v>
+      </c>
+      <c r="H55">
+        <v>403</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K55">
+        <v>132.5</v>
+      </c>
+      <c r="L55">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M55">
+        <v>42.5631234</v>
+      </c>
+      <c r="N55">
+        <v>56.77020993333334</v>
+      </c>
+      <c r="O55">
+        <v>11.35404198666667</v>
+      </c>
+      <c r="P55">
+        <v>45.41616794666668</v>
+      </c>
+      <c r="Q55">
+        <v>177.9161679466667</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1280996999199971</v>
+      </c>
+      <c r="T55">
+        <v>1.529726789075095</v>
+      </c>
+      <c r="U55">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V55">
+        <v>0.2</v>
+      </c>
+      <c r="W55">
+        <v>0.05992</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>2.3337886273011</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.09208176442333288</v>
+      </c>
+      <c r="C56">
+        <v>355.9172940646935</v>
+      </c>
+      <c r="D56">
+        <v>647.8052940646935</v>
+      </c>
+      <c r="E56">
+        <v>-90.21199999999999</v>
+      </c>
+      <c r="F56">
+        <v>578.9880000000001</v>
+      </c>
+      <c r="G56">
+        <v>287.1</v>
+      </c>
+      <c r="H56">
+        <v>403</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K56">
+        <v>132.5</v>
+      </c>
+      <c r="L56">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M56">
+        <v>43.3662012</v>
+      </c>
+      <c r="N56">
+        <v>55.96713213333334</v>
+      </c>
+      <c r="O56">
+        <v>11.19342642666667</v>
+      </c>
+      <c r="P56">
+        <v>44.77370570666668</v>
+      </c>
+      <c r="Q56">
+        <v>177.2737057066667</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1298368791811584</v>
+      </c>
+      <c r="T56">
+        <v>1.55948511587356</v>
+      </c>
+      <c r="U56">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V56">
+        <v>0.2</v>
+      </c>
+      <c r="W56">
+        <v>0.05992</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>2.290570319388117</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.0921990698842671</v>
+      </c>
+      <c r="C57">
+        <v>343.7722149964517</v>
+      </c>
+      <c r="D57">
+        <v>646.3822149964517</v>
+      </c>
+      <c r="E57">
+        <v>-79.49000000000001</v>
+      </c>
+      <c r="F57">
+        <v>589.71</v>
+      </c>
+      <c r="G57">
+        <v>287.1</v>
+      </c>
+      <c r="H57">
+        <v>403</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K57">
+        <v>132.5</v>
+      </c>
+      <c r="L57">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M57">
+        <v>44.169279</v>
+      </c>
+      <c r="N57">
+        <v>55.16405433333335</v>
+      </c>
+      <c r="O57">
+        <v>11.03281086666667</v>
+      </c>
+      <c r="P57">
+        <v>44.13124346666667</v>
+      </c>
+      <c r="Q57">
+        <v>176.6312434666667</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1316512664094824</v>
+      </c>
+      <c r="T57">
+        <v>1.590566034974179</v>
+      </c>
+      <c r="U57">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V57">
+        <v>0.2</v>
+      </c>
+      <c r="W57">
+        <v>0.05992</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>2.248923586308333</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.09231637534520135</v>
+      </c>
+      <c r="C58">
+        <v>331.6333745774066</v>
+      </c>
+      <c r="D58">
+        <v>644.9653745774067</v>
+      </c>
+      <c r="E58">
+        <v>-68.76799999999992</v>
+      </c>
+      <c r="F58">
+        <v>600.4320000000001</v>
+      </c>
+      <c r="G58">
+        <v>287.1</v>
+      </c>
+      <c r="H58">
+        <v>403</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K58">
+        <v>132.5</v>
+      </c>
+      <c r="L58">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M58">
+        <v>44.97235680000001</v>
+      </c>
+      <c r="N58">
+        <v>54.36097653333334</v>
+      </c>
+      <c r="O58">
+        <v>10.87219530666667</v>
+      </c>
+      <c r="P58">
+        <v>43.48878122666667</v>
+      </c>
+      <c r="Q58">
+        <v>175.9887812266667</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1335481257845485</v>
+      </c>
+      <c r="T58">
+        <v>1.623059723124826</v>
+      </c>
+      <c r="U58">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V58">
+        <v>0.2</v>
+      </c>
+      <c r="W58">
+        <v>0.05992</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>2.208764236552827</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.09243368080613557</v>
+      </c>
+      <c r="C59">
+        <v>319.5007318727806</v>
+      </c>
+      <c r="D59">
+        <v>643.5547318727807</v>
+      </c>
+      <c r="E59">
+        <v>-58.04599999999994</v>
+      </c>
+      <c r="F59">
+        <v>611.1540000000001</v>
+      </c>
+      <c r="G59">
+        <v>287.1</v>
+      </c>
+      <c r="H59">
+        <v>403</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K59">
+        <v>132.5</v>
+      </c>
+      <c r="L59">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M59">
+        <v>45.7754346</v>
+      </c>
+      <c r="N59">
+        <v>53.55789873333334</v>
+      </c>
+      <c r="O59">
+        <v>10.71157974666667</v>
+      </c>
+      <c r="P59">
+        <v>42.84631898666667</v>
+      </c>
+      <c r="Q59">
+        <v>175.3463189866667</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1355332111770595</v>
+      </c>
+      <c r="T59">
+        <v>1.657064745608062</v>
+      </c>
+      <c r="U59">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V59">
+        <v>0.2</v>
+      </c>
+      <c r="W59">
+        <v>0.05992</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>2.170013986788742</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.09255098626706978</v>
+      </c>
+      <c r="C60">
+        <v>307.3742463051367</v>
+      </c>
+      <c r="D60">
+        <v>642.1502463051366</v>
+      </c>
+      <c r="E60">
+        <v>-47.32400000000007</v>
+      </c>
+      <c r="F60">
+        <v>621.876</v>
+      </c>
+      <c r="G60">
+        <v>287.1</v>
+      </c>
+      <c r="H60">
+        <v>403</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K60">
+        <v>132.5</v>
+      </c>
+      <c r="L60">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M60">
+        <v>46.57851239999999</v>
+      </c>
+      <c r="N60">
+        <v>52.75482093333335</v>
+      </c>
+      <c r="O60">
+        <v>10.55096418666667</v>
+      </c>
+      <c r="P60">
+        <v>42.20385674666668</v>
+      </c>
+      <c r="Q60">
+        <v>174.7038567466667</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1376128244454042</v>
+      </c>
+      <c r="T60">
+        <v>1.692689054876213</v>
+      </c>
+      <c r="U60">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V60">
+        <v>0.2</v>
+      </c>
+      <c r="W60">
+        <v>0.05992</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>2.132599952533765</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.09266829172800402</v>
+      </c>
+      <c r="C61">
+        <v>295.2538776504891</v>
+      </c>
+      <c r="D61">
+        <v>640.7518776504891</v>
+      </c>
+      <c r="E61">
+        <v>-36.60200000000009</v>
+      </c>
+      <c r="F61">
+        <v>632.598</v>
+      </c>
+      <c r="G61">
+        <v>287.1</v>
+      </c>
+      <c r="H61">
+        <v>403</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K61">
+        <v>132.5</v>
+      </c>
+      <c r="L61">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M61">
+        <v>47.38159019999999</v>
+      </c>
+      <c r="N61">
+        <v>51.95174313333335</v>
+      </c>
+      <c r="O61">
+        <v>10.39034862666667</v>
+      </c>
+      <c r="P61">
+        <v>41.56139450666668</v>
+      </c>
+      <c r="Q61">
+        <v>174.0613945066667</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1397938822634244</v>
+      </c>
+      <c r="T61">
+        <v>1.730051135328177</v>
+      </c>
+      <c r="U61">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V61">
+        <v>0.2</v>
+      </c>
+      <c r="W61">
+        <v>0.05992</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>2.096454190626412</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.09278559718893825</v>
+      </c>
+      <c r="C62">
+        <v>283.1395860344638</v>
+      </c>
+      <c r="D62">
+        <v>639.3595860344639</v>
+      </c>
+      <c r="E62">
+        <v>-25.88</v>
+      </c>
+      <c r="F62">
+        <v>643.3200000000001</v>
+      </c>
+      <c r="G62">
+        <v>287.1</v>
+      </c>
+      <c r="H62">
+        <v>403</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K62">
+        <v>132.5</v>
+      </c>
+      <c r="L62">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M62">
+        <v>48.184668</v>
+      </c>
+      <c r="N62">
+        <v>51.14866533333334</v>
+      </c>
+      <c r="O62">
+        <v>10.22973306666667</v>
+      </c>
+      <c r="P62">
+        <v>40.91893226666667</v>
+      </c>
+      <c r="Q62">
+        <v>173.4189322666667</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1420839929723456</v>
+      </c>
+      <c r="T62">
+        <v>1.769281319802739</v>
+      </c>
+      <c r="U62">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V62">
+        <v>0.2</v>
+      </c>
+      <c r="W62">
+        <v>0.05992</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>2.061513287449305</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.09290290264987248</v>
+      </c>
+      <c r="C63">
+        <v>271.0313319285085</v>
+      </c>
+      <c r="D63">
+        <v>637.9733319285085</v>
+      </c>
+      <c r="E63">
+        <v>-15.15800000000002</v>
+      </c>
+      <c r="F63">
+        <v>654.042</v>
+      </c>
+      <c r="G63">
+        <v>287.1</v>
+      </c>
+      <c r="H63">
+        <v>403</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K63">
+        <v>132.5</v>
+      </c>
+      <c r="L63">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M63">
+        <v>48.9877458</v>
+      </c>
+      <c r="N63">
+        <v>50.34558753333334</v>
+      </c>
+      <c r="O63">
+        <v>10.06911750666667</v>
+      </c>
+      <c r="P63">
+        <v>40.27647002666667</v>
+      </c>
+      <c r="Q63">
+        <v>172.7764700266667</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1444915452560833</v>
+      </c>
+      <c r="T63">
+        <v>1.810523308609329</v>
+      </c>
+      <c r="U63">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V63">
+        <v>0.2</v>
+      </c>
+      <c r="W63">
+        <v>0.05992</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>2.027717987655055</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1011050081108067</v>
+      </c>
+      <c r="C64">
+        <v>176.3237149065982</v>
+      </c>
+      <c r="D64">
+        <v>553.9877149065982</v>
+      </c>
+      <c r="E64">
+        <v>-4.436000000000035</v>
+      </c>
+      <c r="F64">
+        <v>664.764</v>
+      </c>
+      <c r="G64">
+        <v>287.1</v>
+      </c>
+      <c r="H64">
+        <v>403</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K64">
+        <v>132.5</v>
+      </c>
+      <c r="L64">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M64">
+        <v>60.62647680000001</v>
+      </c>
+      <c r="N64">
+        <v>38.70685653333334</v>
+      </c>
+      <c r="O64">
+        <v>7.741371306666668</v>
+      </c>
+      <c r="P64">
+        <v>30.96548522666667</v>
+      </c>
+      <c r="Q64">
+        <v>163.4654852266667</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1470258108179124</v>
+      </c>
+      <c r="T64">
+        <v>1.85393592840574</v>
+      </c>
+      <c r="U64">
+        <v>0.0912</v>
+      </c>
+      <c r="V64">
+        <v>0.2</v>
+      </c>
+      <c r="W64">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>1.638448060589484</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.101352713571741</v>
+      </c>
+      <c r="C65">
+        <v>163.4079526469407</v>
+      </c>
+      <c r="D65">
+        <v>551.7939526469406</v>
+      </c>
+      <c r="E65">
+        <v>6.285999999999945</v>
+      </c>
+      <c r="F65">
+        <v>675.486</v>
+      </c>
+      <c r="G65">
+        <v>287.1</v>
+      </c>
+      <c r="H65">
+        <v>403</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K65">
+        <v>132.5</v>
+      </c>
+      <c r="L65">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M65">
+        <v>61.6043232</v>
+      </c>
+      <c r="N65">
+        <v>37.72901013333334</v>
+      </c>
+      <c r="O65">
+        <v>7.545802026666668</v>
+      </c>
+      <c r="P65">
+        <v>30.18320810666667</v>
+      </c>
+      <c r="Q65">
+        <v>162.6832081066667</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.149697063707408</v>
+      </c>
+      <c r="T65">
+        <v>1.899695176299255</v>
+      </c>
+      <c r="U65">
+        <v>0.0912</v>
+      </c>
+      <c r="V65">
+        <v>0.2</v>
+      </c>
+      <c r="W65">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>1.612440948516635</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1016004190326752</v>
+      </c>
+      <c r="C66">
+        <v>150.5094962237754</v>
+      </c>
+      <c r="D66">
+        <v>549.6174962237754</v>
+      </c>
+      <c r="E66">
+        <v>17.00800000000004</v>
+      </c>
+      <c r="F66">
+        <v>686.2080000000001</v>
+      </c>
+      <c r="G66">
+        <v>287.1</v>
+      </c>
+      <c r="H66">
+        <v>403</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K66">
+        <v>132.5</v>
+      </c>
+      <c r="L66">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M66">
+        <v>62.58216960000001</v>
+      </c>
+      <c r="N66">
+        <v>36.75116373333334</v>
+      </c>
+      <c r="O66">
+        <v>7.350232746666667</v>
+      </c>
+      <c r="P66">
+        <v>29.40093098666667</v>
+      </c>
+      <c r="Q66">
+        <v>161.9009309866667</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1525167195352088</v>
+      </c>
+      <c r="T66">
+        <v>1.947996604631298</v>
+      </c>
+      <c r="U66">
+        <v>0.0912</v>
+      </c>
+      <c r="V66">
+        <v>0.2</v>
+      </c>
+      <c r="W66">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>1.587246558696062</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1018481244936094</v>
+      </c>
+      <c r="C67">
+        <v>137.628141661953</v>
+      </c>
+      <c r="D67">
+        <v>547.4581416619531</v>
+      </c>
+      <c r="E67">
+        <v>27.73000000000002</v>
+      </c>
+      <c r="F67">
+        <v>696.9300000000001</v>
+      </c>
+      <c r="G67">
+        <v>287.1</v>
+      </c>
+      <c r="H67">
+        <v>403</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K67">
+        <v>132.5</v>
+      </c>
+      <c r="L67">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M67">
+        <v>63.56001600000001</v>
+      </c>
+      <c r="N67">
+        <v>35.77331733333333</v>
+      </c>
+      <c r="O67">
+        <v>7.154663466666666</v>
+      </c>
+      <c r="P67">
+        <v>28.61865386666667</v>
+      </c>
+      <c r="Q67">
+        <v>161.1186538666667</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1554974985531697</v>
+      </c>
+      <c r="T67">
+        <v>1.999058114582315</v>
+      </c>
+      <c r="U67">
+        <v>0.0912</v>
+      </c>
+      <c r="V67">
+        <v>0.2</v>
+      </c>
+      <c r="W67">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>1.562827380869969</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1020958299545437</v>
+      </c>
+      <c r="C68">
+        <v>124.7636881793152</v>
+      </c>
+      <c r="D68">
+        <v>545.3156881793152</v>
+      </c>
+      <c r="E68">
+        <v>38.452</v>
+      </c>
+      <c r="F68">
+        <v>707.652</v>
+      </c>
+      <c r="G68">
+        <v>287.1</v>
+      </c>
+      <c r="H68">
+        <v>403</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K68">
+        <v>132.5</v>
+      </c>
+      <c r="L68">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M68">
+        <v>64.53786240000001</v>
+      </c>
+      <c r="N68">
+        <v>34.79547093333333</v>
+      </c>
+      <c r="O68">
+        <v>6.959094186666667</v>
+      </c>
+      <c r="P68">
+        <v>27.83637674666667</v>
+      </c>
+      <c r="Q68">
+        <v>160.3363767466667</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1586536175133637</v>
+      </c>
+      <c r="T68">
+        <v>2.053123242765745</v>
+      </c>
+      <c r="U68">
+        <v>0.0912</v>
+      </c>
+      <c r="V68">
+        <v>0.2</v>
+      </c>
+      <c r="W68">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>1.539148178129515</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1023435354154779</v>
+      </c>
+      <c r="C69">
+        <v>111.9159381244601</v>
+      </c>
+      <c r="D69">
+        <v>543.1899381244601</v>
+      </c>
+      <c r="E69">
+        <v>49.17399999999998</v>
+      </c>
+      <c r="F69">
+        <v>718.374</v>
+      </c>
+      <c r="G69">
+        <v>287.1</v>
+      </c>
+      <c r="H69">
+        <v>403</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K69">
+        <v>132.5</v>
+      </c>
+      <c r="L69">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M69">
+        <v>65.5157088</v>
+      </c>
+      <c r="N69">
+        <v>33.81762453333334</v>
+      </c>
+      <c r="O69">
+        <v>6.763524906666669</v>
+      </c>
+      <c r="P69">
+        <v>27.05409962666668</v>
+      </c>
+      <c r="Q69">
+        <v>159.5540996266667</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.162001016410539</v>
+      </c>
+      <c r="T69">
+        <v>2.110465045384534</v>
+      </c>
+      <c r="U69">
+        <v>0.0912</v>
+      </c>
+      <c r="V69">
+        <v>0.2</v>
+      </c>
+      <c r="W69">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>1.516175817261911</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.141767596339491</v>
+      </c>
+      <c r="C70">
+        <v>-106.781716112663</v>
+      </c>
+      <c r="D70">
+        <v>335.2142838873371</v>
+      </c>
+      <c r="E70">
+        <v>59.89600000000007</v>
+      </c>
+      <c r="F70">
+        <v>729.0960000000001</v>
+      </c>
+      <c r="G70">
+        <v>287.1</v>
+      </c>
+      <c r="H70">
+        <v>403</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K70">
+        <v>132.5</v>
+      </c>
+      <c r="L70">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M70">
+        <v>114.1764336</v>
+      </c>
+      <c r="N70">
+        <v>-14.84310026666668</v>
+      </c>
+      <c r="O70">
+        <v>-2.968620053333336</v>
+      </c>
+      <c r="P70">
+        <v>-11.87448021333335</v>
+      </c>
+      <c r="Q70">
+        <v>120.6255197866667</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1681514930221417</v>
+      </c>
+      <c r="T70">
+        <v>2.215824288996523</v>
+      </c>
+      <c r="U70">
+        <v>0.1566</v>
+      </c>
+      <c r="V70">
+        <v>0.1739997129028093</v>
+      </c>
+      <c r="W70">
+        <v>0.1293516449594201</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.8699985645140462</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.142945596339491</v>
+      </c>
+      <c r="C71">
+        <v>-121.2953543604488</v>
+      </c>
+      <c r="D71">
+        <v>331.4226456395513</v>
+      </c>
+      <c r="E71">
+        <v>70.61800000000005</v>
+      </c>
+      <c r="F71">
+        <v>739.8180000000001</v>
+      </c>
+      <c r="G71">
+        <v>287.1</v>
+      </c>
+      <c r="H71">
+        <v>403</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K71">
+        <v>132.5</v>
+      </c>
+      <c r="L71">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M71">
+        <v>115.8554988</v>
+      </c>
+      <c r="N71">
+        <v>-16.52216546666668</v>
+      </c>
+      <c r="O71">
+        <v>-3.304433093333336</v>
+      </c>
+      <c r="P71">
+        <v>-13.21773237333334</v>
+      </c>
+      <c r="Q71">
+        <v>119.2822676266667</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1723241218293076</v>
+      </c>
+      <c r="T71">
+        <v>2.287302491867379</v>
+      </c>
+      <c r="U71">
+        <v>0.1566</v>
+      </c>
+      <c r="V71">
+        <v>0.1714779779332034</v>
+      </c>
+      <c r="W71">
+        <v>0.1297465486556603</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.8573898896660166</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.144123596339491</v>
+      </c>
+      <c r="C72">
+        <v>-135.7241768592263</v>
+      </c>
+      <c r="D72">
+        <v>327.7158231407738</v>
+      </c>
+      <c r="E72">
+        <v>81.34000000000003</v>
+      </c>
+      <c r="F72">
+        <v>750.5400000000001</v>
+      </c>
+      <c r="G72">
+        <v>287.1</v>
+      </c>
+      <c r="H72">
+        <v>403</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K72">
+        <v>132.5</v>
+      </c>
+      <c r="L72">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M72">
+        <v>117.534564</v>
+      </c>
+      <c r="N72">
+        <v>-18.20123066666669</v>
+      </c>
+      <c r="O72">
+        <v>-3.640246133333338</v>
+      </c>
+      <c r="P72">
+        <v>-14.56098453333335</v>
+      </c>
+      <c r="Q72">
+        <v>117.9390154666666</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1767749258902845</v>
+      </c>
+      <c r="T72">
+        <v>2.363545908262958</v>
+      </c>
+      <c r="U72">
+        <v>0.1566</v>
+      </c>
+      <c r="V72">
+        <v>0.1690282925341576</v>
+      </c>
+      <c r="W72">
+        <v>0.130130169389151</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.8451414626707878</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.145301596339491</v>
+      </c>
+      <c r="C73">
+        <v>-150.0709980161714</v>
+      </c>
+      <c r="D73">
+        <v>324.0910019838285</v>
+      </c>
+      <c r="E73">
+        <v>92.0619999999999</v>
+      </c>
+      <c r="F73">
+        <v>761.2619999999999</v>
+      </c>
+      <c r="G73">
+        <v>287.1</v>
+      </c>
+      <c r="H73">
+        <v>403</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K73">
+        <v>132.5</v>
+      </c>
+      <c r="L73">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M73">
+        <v>119.2136292</v>
+      </c>
+      <c r="N73">
+        <v>-19.88029586666666</v>
+      </c>
+      <c r="O73">
+        <v>-3.976059173333331</v>
+      </c>
+      <c r="P73">
+        <v>-15.90423669333333</v>
+      </c>
+      <c r="Q73">
+        <v>116.5957633066667</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1815326819554667</v>
+      </c>
+      <c r="T73">
+        <v>2.445047491306508</v>
+      </c>
+      <c r="U73">
+        <v>0.1566</v>
+      </c>
+      <c r="V73">
+        <v>0.1666476123576202</v>
+      </c>
+      <c r="W73">
+        <v>0.1305029839047967</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.8332380617881008</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.146479596339491</v>
+      </c>
+      <c r="C74">
+        <v>-164.3385090815482</v>
+      </c>
+      <c r="D74">
+        <v>320.5454909184518</v>
+      </c>
+      <c r="E74">
+        <v>102.784</v>
+      </c>
+      <c r="F74">
+        <v>771.984</v>
+      </c>
+      <c r="G74">
+        <v>287.1</v>
+      </c>
+      <c r="H74">
+        <v>403</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K74">
+        <v>132.5</v>
+      </c>
+      <c r="L74">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M74">
+        <v>120.8926944</v>
+      </c>
+      <c r="N74">
+        <v>-21.55936106666668</v>
+      </c>
+      <c r="O74">
+        <v>-4.311872213333337</v>
+      </c>
+      <c r="P74">
+        <v>-17.24748885333334</v>
+      </c>
+      <c r="Q74">
+        <v>115.2525111466666</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1866302777395905</v>
+      </c>
+      <c r="T74">
+        <v>2.532370615996026</v>
+      </c>
+      <c r="U74">
+        <v>0.1566</v>
+      </c>
+      <c r="V74">
+        <v>0.1643330621859865</v>
+      </c>
+      <c r="W74">
+        <v>0.1308654424616745</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.8216653109299326</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.147657596339491</v>
+      </c>
+      <c r="C75">
+        <v>-178.5292848124058</v>
+      </c>
+      <c r="D75">
+        <v>317.0767151875942</v>
+      </c>
+      <c r="E75">
+        <v>113.506</v>
+      </c>
+      <c r="F75">
+        <v>782.706</v>
+      </c>
+      <c r="G75">
+        <v>287.1</v>
+      </c>
+      <c r="H75">
+        <v>403</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K75">
+        <v>132.5</v>
+      </c>
+      <c r="L75">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M75">
+        <v>122.5717596</v>
+      </c>
+      <c r="N75">
+        <v>-23.23842626666668</v>
+      </c>
+      <c r="O75">
+        <v>-4.647685253333336</v>
+      </c>
+      <c r="P75">
+        <v>-18.59074101333334</v>
+      </c>
+      <c r="Q75">
+        <v>113.9092589866667</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1921054732114272</v>
+      </c>
+      <c r="T75">
+        <v>2.626162120292175</v>
+      </c>
+      <c r="U75">
+        <v>0.1566</v>
+      </c>
+      <c r="V75">
+        <v>0.1620819243478223</v>
+      </c>
+      <c r="W75">
+        <v>0.131217970647131</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.8104096217391117</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1888522942809407</v>
+      </c>
+      <c r="C76">
+        <v>-276.3001338087728</v>
+      </c>
+      <c r="D76">
+        <v>230.0278661912272</v>
+      </c>
+      <c r="E76">
+        <v>124.228</v>
+      </c>
+      <c r="F76">
+        <v>793.428</v>
+      </c>
+      <c r="G76">
+        <v>287.1</v>
+      </c>
+      <c r="H76">
+        <v>403</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K76">
+        <v>132.5</v>
+      </c>
+      <c r="L76">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M76">
+        <v>165.6677664</v>
+      </c>
+      <c r="N76">
+        <v>-66.33443306666666</v>
+      </c>
+      <c r="O76">
+        <v>-13.26688661333333</v>
+      </c>
+      <c r="P76">
+        <v>-53.06754645333333</v>
+      </c>
+      <c r="Q76">
+        <v>79.43245354666666</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2033429834943658</v>
+      </c>
+      <c r="T76">
+        <v>2.818663556889595</v>
+      </c>
+      <c r="U76">
+        <v>0.2088</v>
+      </c>
+      <c r="V76">
+        <v>0.1199187210546388</v>
+      </c>
+      <c r="W76">
+        <v>0.1837609710437914</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.5995936052731942</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1905522942809408</v>
+      </c>
+      <c r="C77">
+        <v>-289.5990132844871</v>
+      </c>
+      <c r="D77">
+        <v>227.450986715513</v>
+      </c>
+      <c r="E77">
+        <v>134.95</v>
+      </c>
+      <c r="F77">
+        <v>804.1500000000001</v>
+      </c>
+      <c r="G77">
+        <v>287.1</v>
+      </c>
+      <c r="H77">
+        <v>403</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K77">
+        <v>132.5</v>
+      </c>
+      <c r="L77">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M77">
+        <v>167.90652</v>
+      </c>
+      <c r="N77">
+        <v>-68.57318666666669</v>
+      </c>
+      <c r="O77">
+        <v>-13.71463733333334</v>
+      </c>
+      <c r="P77">
+        <v>-54.85854933333335</v>
+      </c>
+      <c r="Q77">
+        <v>77.64145066666666</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2099247028341404</v>
+      </c>
+      <c r="T77">
+        <v>2.931410099165179</v>
+      </c>
+      <c r="U77">
+        <v>0.2088</v>
+      </c>
+      <c r="V77">
+        <v>0.1183198047739103</v>
+      </c>
+      <c r="W77">
+        <v>0.1840948247632075</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.5915990238695514</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1922522942809408</v>
+      </c>
+      <c r="C78">
+        <v>-302.8407975550855</v>
+      </c>
+      <c r="D78">
+        <v>224.9312024449145</v>
+      </c>
+      <c r="E78">
+        <v>145.672</v>
+      </c>
+      <c r="F78">
+        <v>814.8720000000001</v>
+      </c>
+      <c r="G78">
+        <v>287.1</v>
+      </c>
+      <c r="H78">
+        <v>403</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K78">
+        <v>132.5</v>
+      </c>
+      <c r="L78">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M78">
+        <v>170.1452736</v>
+      </c>
+      <c r="N78">
+        <v>-70.81194026666668</v>
+      </c>
+      <c r="O78">
+        <v>-14.16238805333334</v>
+      </c>
+      <c r="P78">
+        <v>-56.64955221333334</v>
+      </c>
+      <c r="Q78">
+        <v>75.85044778666665</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.217054898785563</v>
+      </c>
+      <c r="T78">
+        <v>3.053552186630395</v>
+      </c>
+      <c r="U78">
+        <v>0.2088</v>
+      </c>
+      <c r="V78">
+        <v>0.1167629652374115</v>
+      </c>
+      <c r="W78">
+        <v>0.1844198928584285</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.5838148261870575</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1939522942809408</v>
+      </c>
+      <c r="C79">
+        <v>-316.0273633929839</v>
+      </c>
+      <c r="D79">
+        <v>222.4666366070161</v>
+      </c>
+      <c r="E79">
+        <v>156.394</v>
+      </c>
+      <c r="F79">
+        <v>825.5940000000001</v>
+      </c>
+      <c r="G79">
+        <v>287.1</v>
+      </c>
+      <c r="H79">
+        <v>403</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K79">
+        <v>132.5</v>
+      </c>
+      <c r="L79">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M79">
+        <v>172.3840272</v>
+      </c>
+      <c r="N79">
+        <v>-73.05069386666668</v>
+      </c>
+      <c r="O79">
+        <v>-14.61013877333334</v>
+      </c>
+      <c r="P79">
+        <v>-58.44055509333334</v>
+      </c>
+      <c r="Q79">
+        <v>74.05944490666666</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2248051117762396</v>
+      </c>
+      <c r="T79">
+        <v>3.186315325179543</v>
+      </c>
+      <c r="U79">
+        <v>0.2088</v>
+      </c>
+      <c r="V79">
+        <v>0.1152465630914711</v>
+      </c>
+      <c r="W79">
+        <v>0.1847365176265008</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.5762328154573554</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1956522942809408</v>
+      </c>
+      <c r="C80">
+        <v>-329.1605062070923</v>
+      </c>
+      <c r="D80">
+        <v>220.0554937929076</v>
+      </c>
+      <c r="E80">
+        <v>167.116</v>
+      </c>
+      <c r="F80">
+        <v>836.316</v>
+      </c>
+      <c r="G80">
+        <v>287.1</v>
+      </c>
+      <c r="H80">
+        <v>403</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K80">
+        <v>132.5</v>
+      </c>
+      <c r="L80">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M80">
+        <v>174.6227808</v>
+      </c>
+      <c r="N80">
+        <v>-75.28944746666667</v>
+      </c>
+      <c r="O80">
+        <v>-15.05788949333333</v>
+      </c>
+      <c r="P80">
+        <v>-60.23155797333334</v>
+      </c>
+      <c r="Q80">
+        <v>72.26844202666666</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2332598895842505</v>
+      </c>
+      <c r="T80">
+        <v>3.331147839960431</v>
+      </c>
+      <c r="U80">
+        <v>0.2088</v>
+      </c>
+      <c r="V80">
+        <v>0.1137690430518368</v>
+      </c>
+      <c r="W80">
+        <v>0.1850450238107765</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.5688452152591842</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1973522942809408</v>
+      </c>
+      <c r="C81">
+        <v>-342.2419444047201</v>
+      </c>
+      <c r="D81">
+        <v>217.69605559528</v>
+      </c>
+      <c r="E81">
+        <v>177.8380000000001</v>
+      </c>
+      <c r="F81">
+        <v>847.0380000000001</v>
+      </c>
+      <c r="G81">
+        <v>287.1</v>
+      </c>
+      <c r="H81">
+        <v>403</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K81">
+        <v>132.5</v>
+      </c>
+      <c r="L81">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M81">
+        <v>176.8615344</v>
+      </c>
+      <c r="N81">
+        <v>-77.5282010666667</v>
+      </c>
+      <c r="O81">
+        <v>-15.50564021333334</v>
+      </c>
+      <c r="P81">
+        <v>-62.02256085333336</v>
+      </c>
+      <c r="Q81">
+        <v>70.47743914666664</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2425198843263577</v>
+      </c>
+      <c r="T81">
+        <v>3.489773927577595</v>
+      </c>
+      <c r="U81">
+        <v>0.2088</v>
+      </c>
+      <c r="V81">
+        <v>0.1123289285828262</v>
+      </c>
+      <c r="W81">
+        <v>0.1853457197119059</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.5616446429141311</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1990522942809408</v>
+      </c>
+      <c r="C82">
+        <v>-355.2733234758439</v>
+      </c>
+      <c r="D82">
+        <v>215.3866765241562</v>
+      </c>
+      <c r="E82">
+        <v>188.5600000000001</v>
+      </c>
+      <c r="F82">
+        <v>857.7600000000001</v>
+      </c>
+      <c r="G82">
+        <v>287.1</v>
+      </c>
+      <c r="H82">
+        <v>403</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K82">
+        <v>132.5</v>
+      </c>
+      <c r="L82">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M82">
+        <v>179.100288</v>
+      </c>
+      <c r="N82">
+        <v>-79.76695466666669</v>
+      </c>
+      <c r="O82">
+        <v>-15.95339093333334</v>
+      </c>
+      <c r="P82">
+        <v>-63.81356373333335</v>
+      </c>
+      <c r="Q82">
+        <v>68.68643626666665</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2527058785426756</v>
+      </c>
+      <c r="T82">
+        <v>3.664262623956474</v>
+      </c>
+      <c r="U82">
+        <v>0.2088</v>
+      </c>
+      <c r="V82">
+        <v>0.1109248169755409</v>
+      </c>
+      <c r="W82">
+        <v>0.1856388982155071</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.5546240848777045</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2007522942809408</v>
+      </c>
+      <c r="C83">
+        <v>-368.2562198201456</v>
+      </c>
+      <c r="D83">
+        <v>213.1257801798544</v>
+      </c>
+      <c r="E83">
+        <v>199.282</v>
+      </c>
+      <c r="F83">
+        <v>868.4820000000001</v>
+      </c>
+      <c r="G83">
+        <v>287.1</v>
+      </c>
+      <c r="H83">
+        <v>403</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K83">
+        <v>132.5</v>
+      </c>
+      <c r="L83">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M83">
+        <v>181.3390416</v>
+      </c>
+      <c r="N83">
+        <v>-82.00570826666669</v>
+      </c>
+      <c r="O83">
+        <v>-16.40114165333334</v>
+      </c>
+      <c r="P83">
+        <v>-65.60456661333335</v>
+      </c>
+      <c r="Q83">
+        <v>66.89543338666665</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2639640826765006</v>
+      </c>
+      <c r="T83">
+        <v>3.857118551533131</v>
+      </c>
+      <c r="U83">
+        <v>0.2088</v>
+      </c>
+      <c r="V83">
+        <v>0.1095553747906577</v>
+      </c>
+      <c r="W83">
+        <v>0.1859248377437107</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.5477768739532884</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2024522942809408</v>
+      </c>
+      <c r="C84">
+        <v>-381.1921443355195</v>
+      </c>
+      <c r="D84">
+        <v>210.9118556644806</v>
+      </c>
+      <c r="E84">
+        <v>210.004</v>
+      </c>
+      <c r="F84">
+        <v>879.2040000000001</v>
+      </c>
+      <c r="G84">
+        <v>287.1</v>
+      </c>
+      <c r="H84">
+        <v>403</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K84">
+        <v>132.5</v>
+      </c>
+      <c r="L84">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M84">
+        <v>183.5777952</v>
+      </c>
+      <c r="N84">
+        <v>-84.24446186666668</v>
+      </c>
+      <c r="O84">
+        <v>-16.84889237333334</v>
+      </c>
+      <c r="P84">
+        <v>-67.39556949333334</v>
+      </c>
+      <c r="Q84">
+        <v>65.10443050666666</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2764731983807507</v>
+      </c>
+      <c r="T84">
+        <v>4.071402915507194</v>
+      </c>
+      <c r="U84">
+        <v>0.2088</v>
+      </c>
+      <c r="V84">
+        <v>0.1082193336346741</v>
+      </c>
+      <c r="W84">
+        <v>0.1862038031370801</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.5410966681733702</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2041522942809408</v>
+      </c>
+      <c r="C85">
+        <v>-394.0825457852172</v>
+      </c>
+      <c r="D85">
+        <v>208.7434542147829</v>
+      </c>
+      <c r="E85">
+        <v>220.7260000000001</v>
+      </c>
+      <c r="F85">
+        <v>889.9260000000002</v>
+      </c>
+      <c r="G85">
+        <v>287.1</v>
+      </c>
+      <c r="H85">
+        <v>403</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K85">
+        <v>132.5</v>
+      </c>
+      <c r="L85">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M85">
+        <v>185.8165488</v>
+      </c>
+      <c r="N85">
+        <v>-86.48321546666671</v>
+      </c>
+      <c r="O85">
+        <v>-17.29664309333334</v>
+      </c>
+      <c r="P85">
+        <v>-69.18657237333336</v>
+      </c>
+      <c r="Q85">
+        <v>63.31342762666664</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.290453974756089</v>
+      </c>
+      <c r="T85">
+        <v>4.310897204654677</v>
+      </c>
+      <c r="U85">
+        <v>0.2088</v>
+      </c>
+      <c r="V85">
+        <v>0.1069154862414852</v>
+      </c>
+      <c r="W85">
+        <v>0.1864760464727779</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.5345774312074261</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2058522942809408</v>
+      </c>
+      <c r="C86">
+        <v>-406.9288139593992</v>
+      </c>
+      <c r="D86">
+        <v>206.6191860406007</v>
+      </c>
+      <c r="E86">
+        <v>231.448</v>
+      </c>
+      <c r="F86">
+        <v>900.648</v>
+      </c>
+      <c r="G86">
+        <v>287.1</v>
+      </c>
+      <c r="H86">
+        <v>403</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K86">
+        <v>132.5</v>
+      </c>
+      <c r="L86">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M86">
+        <v>188.0553024</v>
+      </c>
+      <c r="N86">
+        <v>-88.72196906666667</v>
+      </c>
+      <c r="O86">
+        <v>-17.74439381333334</v>
+      </c>
+      <c r="P86">
+        <v>-70.97757525333334</v>
+      </c>
+      <c r="Q86">
+        <v>61.52242474666666</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3061823481783444</v>
+      </c>
+      <c r="T86">
+        <v>4.580328279945592</v>
+      </c>
+      <c r="U86">
+        <v>0.2088</v>
+      </c>
+      <c r="V86">
+        <v>0.1056426828338485</v>
+      </c>
+      <c r="W86">
+        <v>0.1867418078242924</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.5282134141692425</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2075522942809408</v>
+      </c>
+      <c r="C87">
+        <v>-419.7322826455924</v>
+      </c>
+      <c r="D87">
+        <v>204.5377173544076</v>
+      </c>
+      <c r="E87">
+        <v>242.17</v>
+      </c>
+      <c r="F87">
+        <v>911.37</v>
+      </c>
+      <c r="G87">
+        <v>287.1</v>
+      </c>
+      <c r="H87">
+        <v>403</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K87">
+        <v>132.5</v>
+      </c>
+      <c r="L87">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M87">
+        <v>190.294056</v>
+      </c>
+      <c r="N87">
+        <v>-90.96072266666667</v>
+      </c>
+      <c r="O87">
+        <v>-18.19214453333333</v>
+      </c>
+      <c r="P87">
+        <v>-72.76857813333334</v>
+      </c>
+      <c r="Q87">
+        <v>59.73142186666666</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3240078380569007</v>
+      </c>
+      <c r="T87">
+        <v>4.885683498608632</v>
+      </c>
+      <c r="U87">
+        <v>0.2088</v>
+      </c>
+      <c r="V87">
+        <v>0.1043998277416856</v>
+      </c>
+      <c r="W87">
+        <v>0.1870013159675361</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.5219991387084278</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2092522942809408</v>
+      </c>
+      <c r="C88">
+        <v>-432.4942324213894</v>
+      </c>
+      <c r="D88">
+        <v>202.4977675786106</v>
+      </c>
+      <c r="E88">
+        <v>252.8919999999999</v>
+      </c>
+      <c r="F88">
+        <v>922.092</v>
+      </c>
+      <c r="G88">
+        <v>287.1</v>
+      </c>
+      <c r="H88">
+        <v>403</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K88">
+        <v>132.5</v>
+      </c>
+      <c r="L88">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M88">
+        <v>192.5328096</v>
+      </c>
+      <c r="N88">
+        <v>-93.19947626666666</v>
+      </c>
+      <c r="O88">
+        <v>-18.63989525333333</v>
+      </c>
+      <c r="P88">
+        <v>-74.55958101333333</v>
+      </c>
+      <c r="Q88">
+        <v>57.94041898666667</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3443798264895365</v>
+      </c>
+      <c r="T88">
+        <v>5.234660891366391</v>
+      </c>
+      <c r="U88">
+        <v>0.2088</v>
+      </c>
+      <c r="V88">
+        <v>0.1031858762563171</v>
+      </c>
+      <c r="W88">
+        <v>0.187254789037681</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.5159293812815857</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2109522942809408</v>
+      </c>
+      <c r="C89">
+        <v>-445.2158932816848</v>
+      </c>
+      <c r="D89">
+        <v>200.4981067183153</v>
+      </c>
+      <c r="E89">
+        <v>263.614</v>
+      </c>
+      <c r="F89">
+        <v>932.8140000000001</v>
+      </c>
+      <c r="G89">
+        <v>287.1</v>
+      </c>
+      <c r="H89">
+        <v>403</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K89">
+        <v>132.5</v>
+      </c>
+      <c r="L89">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M89">
+        <v>194.7715632</v>
+      </c>
+      <c r="N89">
+        <v>-95.43822986666669</v>
+      </c>
+      <c r="O89">
+        <v>-19.08764597333334</v>
+      </c>
+      <c r="P89">
+        <v>-76.35058389333335</v>
+      </c>
+      <c r="Q89">
+        <v>56.14941610666665</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3678859669887315</v>
+      </c>
+      <c r="T89">
+        <v>5.63732711377919</v>
+      </c>
+      <c r="U89">
+        <v>0.2088</v>
+      </c>
+      <c r="V89">
+        <v>0.1019998317016468</v>
+      </c>
+      <c r="W89">
+        <v>0.1875024351406961</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.5099991585082341</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2126522942809408</v>
+      </c>
+      <c r="C90">
+        <v>-457.8984471117674</v>
+      </c>
+      <c r="D90">
+        <v>198.5375528882327</v>
+      </c>
+      <c r="E90">
+        <v>274.336</v>
+      </c>
+      <c r="F90">
+        <v>943.5360000000001</v>
+      </c>
+      <c r="G90">
+        <v>287.1</v>
+      </c>
+      <c r="H90">
+        <v>403</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K90">
+        <v>132.5</v>
+      </c>
+      <c r="L90">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M90">
+        <v>197.0103168</v>
+      </c>
+      <c r="N90">
+        <v>-97.67698346666668</v>
+      </c>
+      <c r="O90">
+        <v>-19.53539669333334</v>
+      </c>
+      <c r="P90">
+        <v>-78.14158677333334</v>
+      </c>
+      <c r="Q90">
+        <v>54.35841322666666</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3953097975711259</v>
+      </c>
+      <c r="T90">
+        <v>6.107104373260791</v>
+      </c>
+      <c r="U90">
+        <v>0.2088</v>
+      </c>
+      <c r="V90">
+        <v>0.1008407427050372</v>
+      </c>
+      <c r="W90">
+        <v>0.1877444529231883</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.504203713525186</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2415756729020901</v>
+      </c>
+      <c r="C91">
+        <v>-496.9393116506882</v>
+      </c>
+      <c r="D91">
+        <v>170.2186883493118</v>
+      </c>
+      <c r="E91">
+        <v>285.058</v>
+      </c>
+      <c r="F91">
+        <v>954.258</v>
+      </c>
+      <c r="G91">
+        <v>287.1</v>
+      </c>
+      <c r="H91">
+        <v>403</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K91">
+        <v>132.5</v>
+      </c>
+      <c r="L91">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M91">
+        <v>227.8768104</v>
+      </c>
+      <c r="N91">
+        <v>-128.5434770666667</v>
+      </c>
+      <c r="O91">
+        <v>-25.70869541333333</v>
+      </c>
+      <c r="P91">
+        <v>-102.8347816533333</v>
+      </c>
+      <c r="Q91">
+        <v>29.66521834666666</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4324777666334956</v>
+      </c>
+      <c r="T91">
+        <v>6.743801226902614</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.08718160760541639</v>
+      </c>
+      <c r="W91">
+        <v>0.2179810321038266</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.4359080380270819</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2435756729020902</v>
+      </c>
+      <c r="C92">
+        <v>-509.3238010073287</v>
+      </c>
+      <c r="D92">
+        <v>168.5561989926713</v>
+      </c>
+      <c r="E92">
+        <v>295.78</v>
+      </c>
+      <c r="F92">
+        <v>964.98</v>
+      </c>
+      <c r="G92">
+        <v>287.1</v>
+      </c>
+      <c r="H92">
+        <v>403</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K92">
+        <v>132.5</v>
+      </c>
+      <c r="L92">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M92">
+        <v>230.437224</v>
+      </c>
+      <c r="N92">
+        <v>-131.1038906666667</v>
+      </c>
+      <c r="O92">
+        <v>-26.22077813333334</v>
+      </c>
+      <c r="P92">
+        <v>-104.8831125333333</v>
+      </c>
+      <c r="Q92">
+        <v>27.61688746666667</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4718455432968452</v>
+      </c>
+      <c r="T92">
+        <v>7.418181349592878</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.08621292307646733</v>
+      </c>
+      <c r="W92">
+        <v>0.2182123539693396</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.4310646153823365</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2455756729020902</v>
+      </c>
+      <c r="C93">
+        <v>-521.6761301135239</v>
+      </c>
+      <c r="D93">
+        <v>166.9258698864762</v>
+      </c>
+      <c r="E93">
+        <v>306.5020000000001</v>
+      </c>
+      <c r="F93">
+        <v>975.7020000000001</v>
+      </c>
+      <c r="G93">
+        <v>287.1</v>
+      </c>
+      <c r="H93">
+        <v>403</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K93">
+        <v>132.5</v>
+      </c>
+      <c r="L93">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M93">
+        <v>232.9976376</v>
+      </c>
+      <c r="N93">
+        <v>-133.6643042666667</v>
+      </c>
+      <c r="O93">
+        <v>-26.73286085333334</v>
+      </c>
+      <c r="P93">
+        <v>-106.9314434133334</v>
+      </c>
+      <c r="Q93">
+        <v>25.56855658666663</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5199617147742726</v>
+      </c>
+      <c r="T93">
+        <v>8.242423721769866</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.08526552831738525</v>
+      </c>
+      <c r="W93">
+        <v>0.2184385918378084</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.4263276415869263</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2475756729020902</v>
+      </c>
+      <c r="C94">
+        <v>-533.997223222085</v>
+      </c>
+      <c r="D94">
+        <v>165.326776777915</v>
+      </c>
+      <c r="E94">
+        <v>317.224</v>
+      </c>
+      <c r="F94">
+        <v>986.4240000000001</v>
+      </c>
+      <c r="G94">
+        <v>287.1</v>
+      </c>
+      <c r="H94">
+        <v>403</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K94">
+        <v>132.5</v>
+      </c>
+      <c r="L94">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M94">
+        <v>235.5580512</v>
+      </c>
+      <c r="N94">
+        <v>-136.2247178666667</v>
+      </c>
+      <c r="O94">
+        <v>-27.24494357333334</v>
+      </c>
+      <c r="P94">
+        <v>-108.9797742933333</v>
+      </c>
+      <c r="Q94">
+        <v>23.52022570666665</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5801069291210568</v>
+      </c>
+      <c r="T94">
+        <v>9.272726686991101</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.08433872909654411</v>
+      </c>
+      <c r="W94">
+        <v>0.2186599114917453</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.4216936454827206</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2495756729020902</v>
+      </c>
+      <c r="C95">
+        <v>-546.2879695057675</v>
+      </c>
+      <c r="D95">
+        <v>163.7580304942326</v>
+      </c>
+      <c r="E95">
+        <v>327.946</v>
+      </c>
+      <c r="F95">
+        <v>997.1460000000001</v>
+      </c>
+      <c r="G95">
+        <v>287.1</v>
+      </c>
+      <c r="H95">
+        <v>403</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K95">
+        <v>132.5</v>
+      </c>
+      <c r="L95">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M95">
+        <v>238.1184648</v>
+      </c>
+      <c r="N95">
+        <v>-138.7851314666667</v>
+      </c>
+      <c r="O95">
+        <v>-27.75702629333334</v>
+      </c>
+      <c r="P95">
+        <v>-111.0281051733333</v>
+      </c>
+      <c r="Q95">
+        <v>21.47189482666666</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6574364904240648</v>
+      </c>
+      <c r="T95">
+        <v>10.59740192798983</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.08343186104174256</v>
+      </c>
+      <c r="W95">
+        <v>0.2188764715832319</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.4171593052087128</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2515756729020902</v>
+      </c>
+      <c r="C96">
+        <v>-558.5492247059574</v>
+      </c>
+      <c r="D96">
+        <v>162.2187752940427</v>
+      </c>
+      <c r="E96">
+        <v>338.668</v>
+      </c>
+      <c r="F96">
+        <v>1007.868</v>
+      </c>
+      <c r="G96">
+        <v>287.1</v>
+      </c>
+      <c r="H96">
+        <v>403</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K96">
+        <v>132.5</v>
+      </c>
+      <c r="L96">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M96">
+        <v>240.6788784</v>
+      </c>
+      <c r="N96">
+        <v>-141.3455450666667</v>
+      </c>
+      <c r="O96">
+        <v>-28.26910901333334</v>
+      </c>
+      <c r="P96">
+        <v>-113.0764360533334</v>
+      </c>
+      <c r="Q96">
+        <v>19.42356394666665</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7605425721614092</v>
+      </c>
+      <c r="T96">
+        <v>12.3636355826548</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.0825442880519368</v>
+      </c>
+      <c r="W96">
+        <v>0.2190884240131975</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.4127214402596839</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2535756729020902</v>
+      </c>
+      <c r="C97">
+        <v>-570.7818126892437</v>
+      </c>
+      <c r="D97">
+        <v>160.7081873107565</v>
+      </c>
+      <c r="E97">
+        <v>349.3900000000001</v>
+      </c>
+      <c r="F97">
+        <v>1018.59</v>
+      </c>
+      <c r="G97">
+        <v>287.1</v>
+      </c>
+      <c r="H97">
+        <v>403</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K97">
+        <v>132.5</v>
+      </c>
+      <c r="L97">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M97">
+        <v>243.239292</v>
+      </c>
+      <c r="N97">
+        <v>-143.9059586666667</v>
+      </c>
+      <c r="O97">
+        <v>-28.78119173333334</v>
+      </c>
+      <c r="P97">
+        <v>-115.1247669333333</v>
+      </c>
+      <c r="Q97">
+        <v>17.37523306666665</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.9048910865936917</v>
+      </c>
+      <c r="T97">
+        <v>14.83636269918578</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.08167540080928481</v>
+      </c>
+      <c r="W97">
+        <v>0.2192959142867428</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.4083770040464241</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2555756729020902</v>
+      </c>
+      <c r="C98">
+        <v>-582.9865269178215</v>
+      </c>
+      <c r="D98">
+        <v>159.2254730821784</v>
+      </c>
+      <c r="E98">
+        <v>360.1119999999999</v>
+      </c>
+      <c r="F98">
+        <v>1029.312</v>
+      </c>
+      <c r="G98">
+        <v>287.1</v>
+      </c>
+      <c r="H98">
+        <v>403</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K98">
+        <v>132.5</v>
+      </c>
+      <c r="L98">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M98">
+        <v>245.7997056</v>
+      </c>
+      <c r="N98">
+        <v>-146.4663722666666</v>
+      </c>
+      <c r="O98">
+        <v>-29.29327445333333</v>
+      </c>
+      <c r="P98">
+        <v>-117.1730978133333</v>
+      </c>
+      <c r="Q98">
+        <v>15.32690218666669</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.121413858242112</v>
+      </c>
+      <c r="T98">
+        <v>18.54545337398218</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.08082461538418811</v>
+      </c>
+      <c r="W98">
+        <v>0.2194990818462559</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.4041230769209406</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2575756729020902</v>
+      </c>
+      <c r="C99">
+        <v>-595.1641318392467</v>
+      </c>
+      <c r="D99">
+        <v>157.7698681607534</v>
+      </c>
+      <c r="E99">
+        <v>370.8340000000001</v>
+      </c>
+      <c r="F99">
+        <v>1040.034</v>
+      </c>
+      <c r="G99">
+        <v>287.1</v>
+      </c>
+      <c r="H99">
+        <v>403</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K99">
+        <v>132.5</v>
+      </c>
+      <c r="L99">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M99">
+        <v>248.3601192</v>
+      </c>
+      <c r="N99">
+        <v>-149.0267858666667</v>
+      </c>
+      <c r="O99">
+        <v>-29.80535717333334</v>
+      </c>
+      <c r="P99">
+        <v>-119.2214286933334</v>
+      </c>
+      <c r="Q99">
+        <v>13.27857130666663</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.482285144322816</v>
+      </c>
+      <c r="T99">
+        <v>24.72727116530957</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.07999137192661915</v>
+      </c>
+      <c r="W99">
+        <v>0.2196980603839233</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3999568596330957</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2595756729020902</v>
+      </c>
+      <c r="C100">
+        <v>-607.3153642006466</v>
+      </c>
+      <c r="D100">
+        <v>156.3406357993535</v>
+      </c>
+      <c r="E100">
+        <v>381.556</v>
+      </c>
+      <c r="F100">
+        <v>1050.756</v>
+      </c>
+      <c r="G100">
+        <v>287.1</v>
+      </c>
+      <c r="H100">
+        <v>403</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K100">
+        <v>132.5</v>
+      </c>
+      <c r="L100">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M100">
+        <v>250.9205328</v>
+      </c>
+      <c r="N100">
+        <v>-151.5871994666667</v>
+      </c>
+      <c r="O100">
+        <v>-30.31743989333334</v>
+      </c>
+      <c r="P100">
+        <v>-121.2697595733334</v>
+      </c>
+      <c r="Q100">
+        <v>11.23024042666664</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.204027716484224</v>
+      </c>
+      <c r="T100">
+        <v>37.09090674796435</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.07917513343757202</v>
+      </c>
+      <c r="W100">
+        <v>0.2198929781351078</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.39587566718786</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2615756729020902</v>
+      </c>
+      <c r="C101">
+        <v>-619.4409342921444</v>
+      </c>
+      <c r="D101">
+        <v>154.9370657078556</v>
+      </c>
+      <c r="E101">
+        <v>392.278</v>
+      </c>
+      <c r="F101">
+        <v>1061.478</v>
+      </c>
+      <c r="G101">
+        <v>287.1</v>
+      </c>
+      <c r="H101">
+        <v>403</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>231.8333333333333</v>
+      </c>
+      <c r="K101">
+        <v>132.5</v>
+      </c>
+      <c r="L101">
+        <v>99.33333333333334</v>
+      </c>
+      <c r="M101">
+        <v>253.4809464</v>
+      </c>
+      <c r="N101">
+        <v>-154.1476130666667</v>
+      </c>
+      <c r="O101">
+        <v>-30.82952261333334</v>
+      </c>
+      <c r="P101">
+        <v>-123.3180904533333</v>
+      </c>
+      <c r="Q101">
+        <v>9.18190954666666</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.369255432968449</v>
+      </c>
+      <c r="T101">
+        <v>74.18181349592871</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.07837538461497029</v>
+      </c>
+      <c r="W101">
+        <v>0.2200839581539451</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3918769230748514</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
